--- a/data/MetalliCan/pre_cleaned_data/material_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/material_df.xlsx
@@ -61,294 +61,315 @@
     <t>needs_density</t>
   </si>
   <si>
-    <t>TECH-aa76f6f2-2023-1</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023-1</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023-2</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023-2</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023-3</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023-3</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-2</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-3</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023-4</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-4</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023-2</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023-3</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023-2</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-5</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023-5</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-6</t>
-  </si>
-  <si>
-    <t>TECH-cb85213a-2023-4</t>
-  </si>
-  <si>
-    <t>TECH-9de9bb0d-2023-4</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-10</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023-8</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023-9</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-11</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-13</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023-7</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023-8</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023-7</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-14</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023-9</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023-8</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023-8</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023-10</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023-10</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023-9</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023-11</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-15</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023-9</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023-11</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023-10</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-16</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023-10</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023-12</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023-12</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023-14</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023-12</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023-13</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023-14</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-19</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023-13</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023-15</t>
-  </si>
-  <si>
-    <t>TECH-b86f7d07-2023-5</t>
-  </si>
-  <si>
-    <t>TECH-44857446-2023-5</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023-14</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023-15</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023-16</t>
-  </si>
-  <si>
-    <t>TECH-687b8c8d-2023-6</t>
-  </si>
-  <si>
-    <t>TECH-7607a50e-2023-7</t>
-  </si>
-  <si>
-    <t>TECH-687b8c8d-2023-7</t>
-  </si>
-  <si>
-    <t>TECH-7607a50e-2023-8</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023-20</t>
+    <t>TECH-b86f7d07-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-cb85213a-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-12.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-13.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-44857446-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-9de9bb0d-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-11.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-13.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-15.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-12.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-12.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-15.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-16.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-11.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-11.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-13.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-15.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-16.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-19.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-20.0</t>
+  </si>
+  <si>
+    <t>TECH-7607a50e-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-7607a50e-2023.0-8.0</t>
   </si>
   <si>
     <t>Material use</t>
   </si>
   <si>
+    <t>Surface/underground emulsion &amp; ANFO</t>
+  </si>
+  <si>
+    <t>Explosives</t>
+  </si>
+  <si>
+    <t>Cement</t>
+  </si>
+  <si>
+    <t>Grinding media</t>
+  </si>
+  <si>
+    <t>Lime</t>
+  </si>
+  <si>
+    <t>Lubricants</t>
+  </si>
+  <si>
+    <t>Nitric acid (HNO3)</t>
+  </si>
+  <si>
+    <t>Sodium cyanide (NaCN)</t>
+  </si>
+  <si>
+    <t>Sulfuric acid (H2SO4)</t>
+  </si>
+  <si>
+    <t>Tires</t>
+  </si>
+  <si>
+    <t>Total blasting agents used e.g. ANFO</t>
+  </si>
+  <si>
+    <t>Total sodium cyanide used</t>
+  </si>
+  <si>
+    <t>Hydrochloric acid (HCL)</t>
+  </si>
+  <si>
     <t>2'' balls</t>
   </si>
   <si>
+    <t>3/4'' balls</t>
+  </si>
+  <si>
+    <t>Anti-scalant</t>
+  </si>
+  <si>
+    <t>Flocculant</t>
+  </si>
+  <si>
+    <t>Polyfroth h57</t>
+  </si>
+  <si>
+    <t>S60 SAG Balls</t>
+  </si>
+  <si>
     <t>2.5'' balls</t>
   </si>
   <si>
-    <t>3/4'' balls</t>
-  </si>
-  <si>
     <t>5.5'' balls</t>
   </si>
   <si>
-    <t>Anti-scalant</t>
+    <t>Caustic soda</t>
+  </si>
+  <si>
+    <t>Cyanide</t>
   </si>
   <si>
     <t>Carbon</t>
   </si>
   <si>
-    <t>Caustic soda</t>
-  </si>
-  <si>
-    <t>Cement</t>
-  </si>
-  <si>
     <t>Compressor oil</t>
   </si>
   <si>
-    <t>Cyanide</t>
-  </si>
-  <si>
-    <t>Explosives</t>
-  </si>
-  <si>
-    <t>Flocculant</t>
-  </si>
-  <si>
     <t>Grease</t>
   </si>
   <si>
-    <t>Grinding media</t>
-  </si>
-  <si>
     <t>Hydraulic oil</t>
   </si>
   <si>
-    <t>Hydrochloric acid (HCL)</t>
-  </si>
-  <si>
-    <t>Lime</t>
-  </si>
-  <si>
-    <t>Lubricants</t>
-  </si>
-  <si>
     <t>Motor/drill oil</t>
   </si>
   <si>
-    <t>Nitric acid (HNO3)</t>
-  </si>
-  <si>
-    <t>Polyfroth h57</t>
-  </si>
-  <si>
-    <t>S60 SAG Balls</t>
-  </si>
-  <si>
-    <t>Sodium cyanide (NaCN)</t>
-  </si>
-  <si>
     <t>Sulfur dioxide</t>
   </si>
   <si>
-    <t>Sulfuric acid (H2SO4)</t>
-  </si>
-  <si>
-    <t>Surface/underground emulsion &amp; ANFO</t>
-  </si>
-  <si>
-    <t>Tires</t>
-  </si>
-  <si>
-    <t>Total blasting agents used e.g. ANFO</t>
-  </si>
-  <si>
-    <t>Total sodium cyanide used</t>
-  </si>
-  <si>
     <t>Transmission oil</t>
   </si>
   <si>
+    <t>pounds</t>
+  </si>
+  <si>
     <t>t</t>
   </si>
   <si>
+    <t>kl</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
     <t>kg</t>
   </si>
   <si>
-    <t>kl</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>Explosives, treated as material input because in t</t>
   </si>
   <si>
+    <t>QC-MAIN-b86f7d07</t>
+  </si>
+  <si>
+    <t>ON-MAIN-cb85213a</t>
+  </si>
+  <si>
+    <t>QC-MAIN-6dc537e6</t>
+  </si>
+  <si>
+    <t>ON-MAIN-687b8c8d</t>
+  </si>
+  <si>
+    <t>YT-MAIN-44857446</t>
+  </si>
+  <si>
+    <t>QC-MAIN-9de9bb0d</t>
+  </si>
+  <si>
+    <t>ON-MAIN-fefeaee4</t>
+  </si>
+  <si>
     <t>BC-MAIN-aa76f6f2</t>
   </si>
   <si>
@@ -358,97 +379,76 @@
     <t>QC-MAIN-02884fb5</t>
   </si>
   <si>
-    <t>QC-MAIN-6dc537e6</t>
-  </si>
-  <si>
-    <t>ON-MAIN-fefeaee4</t>
-  </si>
-  <si>
-    <t>ON-MAIN-cb85213a</t>
-  </si>
-  <si>
-    <t>QC-MAIN-9de9bb0d</t>
-  </si>
-  <si>
-    <t>QC-MAIN-b86f7d07</t>
-  </si>
-  <si>
-    <t>YT-MAIN-44857446</t>
-  </si>
-  <si>
-    <t>ON-MAIN-687b8c8d</t>
-  </si>
-  <si>
     <t>ON-MAIN-7607a50e</t>
   </si>
   <si>
     <t>GRP-0d911886</t>
   </si>
   <si>
+    <t>CMP-7e360a1f</t>
+  </si>
+  <si>
+    <t>CMP-3d2c4955</t>
+  </si>
+  <si>
+    <t>CMP-4a434d72</t>
+  </si>
+  <si>
+    <t>CMP-3a4ccc7f</t>
+  </si>
+  <si>
     <t>CMP-d94be190</t>
   </si>
   <si>
     <t>CMP-3d0a95b7</t>
   </si>
   <si>
-    <t>CMP-4a434d72</t>
-  </si>
-  <si>
-    <t>CMP-3d2c4955</t>
-  </si>
-  <si>
-    <t>CMP-7e360a1f</t>
-  </si>
-  <si>
-    <t>CMP-3a4ccc7f</t>
-  </si>
-  <si>
-    <t>SRC_NewGoldInc_2023-New-Gold-ESG-Data-Factbook</t>
-  </si>
-  <si>
-    <t>SRC_IAMGOLDCorporation_2023_iamgold-esg-performance-data-final_protected</t>
-  </si>
-  <si>
-    <t>SRC_NewmontCorporation_Newmont-2023-Performance-Data-Tables-V4-locked</t>
-  </si>
-  <si>
-    <t>SRC_WesdomeGoldMinesLtd._ESG_data_2023</t>
-  </si>
-  <si>
-    <t>SRC_HeclaMiningCompany_SR_2023</t>
-  </si>
-  <si>
-    <t>SRC_AlamosGoldInc_Data_2023</t>
+    <t>HeclaMiningCompany_SR_2023</t>
+  </si>
+  <si>
+    <t>WesdomeGoldMinesLtd._ESG_data_2023</t>
+  </si>
+  <si>
+    <t>NewmontCorporation_Newmont-2023-Performance-Data-Tables-V4-locked</t>
+  </si>
+  <si>
+    <t>AlamosGoldInc_Data_2023</t>
+  </si>
+  <si>
+    <t>NewGoldInc_2023-New-Gold-ESG-Data-Factbook</t>
+  </si>
+  <si>
+    <t>IAMGOLDCorporation_2023_iamgold-esg-performance-data-final_protected</t>
+  </si>
+  <si>
+    <t>lbs→t</t>
+  </si>
+  <si>
+    <t>L×density→t</t>
   </si>
   <si>
     <t>kg→t</t>
   </si>
   <si>
-    <t>L×density→t</t>
-  </si>
-  <si>
-    <t>lbs→t</t>
+    <t>lbs×0.453592/1000</t>
   </si>
   <si>
     <t>reported in tonnes</t>
   </si>
   <si>
+    <t>kl×density=0.88 kg/L</t>
+  </si>
+  <si>
+    <t>l×density=1.51 kg/L</t>
+  </si>
+  <si>
+    <t>l×density=1.84 kg/L</t>
+  </si>
+  <si>
+    <t>kl×density=1.19 kg/L</t>
+  </si>
+  <si>
     <t>kg/1000</t>
-  </si>
-  <si>
-    <t>kl×density=1.19 kg/L</t>
-  </si>
-  <si>
-    <t>kl×density=0.88 kg/L</t>
-  </si>
-  <si>
-    <t>l×density=1.51 kg/L</t>
-  </si>
-  <si>
-    <t>l×density=1.84 kg/L</t>
-  </si>
-  <si>
-    <t>lbs×0.453592/1000</t>
   </si>
 </sst>
 </file>
@@ -873,7 +873,10 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>980</v>
+        <v>6543598</v>
+      </c>
+      <c r="G2" t="s">
+        <v>110</v>
       </c>
       <c r="H2" t="s">
         <v>111</v>
@@ -885,10 +888,10 @@
         <v>129</v>
       </c>
       <c r="L2">
-        <v>980</v>
+        <v>2968.123704016</v>
       </c>
       <c r="M2" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="N2" t="s">
         <v>138</v>
@@ -911,28 +914,31 @@
         <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F3">
-        <v>5977.02</v>
+        <v>1211</v>
+      </c>
+      <c r="G3" t="s">
+        <v>110</v>
       </c>
       <c r="H3" t="s">
         <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L3">
-        <v>5977.02</v>
+        <v>1211</v>
       </c>
       <c r="M3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -952,28 +958,28 @@
         <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F4">
-        <v>179</v>
+        <v>27374</v>
       </c>
       <c r="H4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L4">
-        <v>179</v>
+        <v>27374</v>
       </c>
       <c r="M4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -993,28 +999,31 @@
         <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F5">
-        <v>2819.39</v>
+        <v>3039.9</v>
+      </c>
+      <c r="G5" t="s">
+        <v>110</v>
       </c>
       <c r="H5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L5">
-        <v>2819.39</v>
+        <v>3039.9</v>
       </c>
       <c r="M5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
@@ -1037,22 +1046,22 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>38000</v>
+        <v>2229</v>
       </c>
       <c r="H6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L6">
-        <v>38</v>
+        <v>2229</v>
       </c>
       <c r="M6" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="N6" t="s">
         <v>139</v>
@@ -1072,31 +1081,31 @@
         <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>231239.82</v>
+        <v>380.687</v>
       </c>
       <c r="H7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L7">
-        <v>231.23982</v>
+        <v>335.00456</v>
       </c>
       <c r="M7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
@@ -1113,31 +1122,31 @@
         <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F8">
-        <v>35.4</v>
+        <v>26575</v>
       </c>
       <c r="H8" t="s">
         <v>113</v>
       </c>
       <c r="J8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8">
-        <v>35.4</v>
+        <v>40.12825</v>
       </c>
       <c r="M8" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -1154,31 +1163,31 @@
         <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F9">
-        <v>60.4</v>
+        <v>838.8</v>
       </c>
       <c r="H9" t="s">
         <v>113</v>
       </c>
       <c r="J9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L9">
-        <v>60.4</v>
+        <v>838.8</v>
       </c>
       <c r="M9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -1195,31 +1204,31 @@
         <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F10">
-        <v>526.21</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L10">
-        <v>526.21</v>
+        <v>0.1360864</v>
       </c>
       <c r="M10" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
@@ -1236,31 +1245,31 @@
         <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F11">
-        <v>86.59999999999999</v>
+        <v>241.250566996281</v>
       </c>
       <c r="H11" t="s">
         <v>113</v>
       </c>
       <c r="J11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L11">
-        <v>86.59999999999999</v>
+        <v>241.250566996281</v>
       </c>
       <c r="M11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
@@ -1277,31 +1286,31 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F12">
-        <v>27374</v>
+        <v>486.3</v>
       </c>
       <c r="H12" t="s">
         <v>114</v>
       </c>
       <c r="J12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L12">
-        <v>27374</v>
+        <v>486.3</v>
       </c>
       <c r="M12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -1318,31 +1327,31 @@
         <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F13">
-        <v>9417.6</v>
+        <v>245</v>
       </c>
       <c r="H13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L13">
-        <v>9417.6</v>
+        <v>245</v>
       </c>
       <c r="M13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -1359,28 +1368,31 @@
         <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>105</v>
       </c>
       <c r="F14">
-        <v>12578</v>
-      </c>
-      <c r="I14" t="s">
-        <v>122</v>
+        <v>511210</v>
+      </c>
+      <c r="G14" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" t="s">
+        <v>115</v>
       </c>
       <c r="J14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L14">
-        <v>12578</v>
+        <v>231.88076632</v>
       </c>
       <c r="M14" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="N14" t="s">
         <v>138</v>
@@ -1400,16 +1412,19 @@
         <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F15">
-        <v>1.5</v>
+        <v>506</v>
+      </c>
+      <c r="G15" t="s">
+        <v>110</v>
       </c>
       <c r="H15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J15" t="s">
         <v>124</v>
@@ -1418,13 +1433,13 @@
         <v>130</v>
       </c>
       <c r="L15">
-        <v>1.5</v>
+        <v>506</v>
       </c>
       <c r="M15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
@@ -1441,31 +1456,31 @@
         <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F16">
-        <v>2269.57</v>
+        <v>9417.6</v>
       </c>
       <c r="H16" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K16" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L16">
-        <v>2269.57</v>
+        <v>9417.6</v>
       </c>
       <c r="M16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -1482,31 +1497,34 @@
         <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F17">
-        <v>399.3</v>
+        <v>726.071</v>
+      </c>
+      <c r="G17" t="s">
+        <v>110</v>
       </c>
       <c r="H17" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L17">
-        <v>399.3</v>
+        <v>726.071</v>
       </c>
       <c r="M17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -1523,34 +1541,31 @@
         <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F18">
-        <v>1211</v>
-      </c>
-      <c r="G18" t="s">
-        <v>110</v>
+        <v>57.2</v>
       </c>
       <c r="H18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L18">
-        <v>1211</v>
+        <v>68.068</v>
       </c>
       <c r="M18" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N18" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -1567,34 +1582,31 @@
         <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F19">
-        <v>506</v>
-      </c>
-      <c r="G19" t="s">
-        <v>110</v>
+        <v>924.081</v>
       </c>
       <c r="H19" t="s">
         <v>117</v>
       </c>
       <c r="J19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L19">
-        <v>506</v>
+        <v>924.081</v>
       </c>
       <c r="M19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -1611,34 +1623,31 @@
         <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F20">
-        <v>1483.4</v>
-      </c>
-      <c r="G20" t="s">
-        <v>110</v>
+        <v>336.521</v>
       </c>
       <c r="H20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L20">
-        <v>1483.4</v>
+        <v>296.13848</v>
       </c>
       <c r="M20" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -1655,31 +1664,31 @@
         <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F21">
-        <v>192</v>
+        <v>390.003</v>
       </c>
       <c r="H21" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K21" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L21">
-        <v>192</v>
+        <v>390.003</v>
       </c>
       <c r="M21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -1696,31 +1705,31 @@
         <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F22">
-        <v>149.1</v>
+        <v>100.705343372947</v>
       </c>
       <c r="H22" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L22">
-        <v>149.1</v>
+        <v>100.705343372947</v>
       </c>
       <c r="M22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -1737,31 +1746,31 @@
         <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F23">
-        <v>46.2</v>
+        <v>980</v>
       </c>
       <c r="H23" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J23" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K23" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L23">
-        <v>46.2</v>
+        <v>980</v>
       </c>
       <c r="M23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -1778,31 +1787,31 @@
         <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F24">
-        <v>4.5</v>
+        <v>179</v>
       </c>
       <c r="H24" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K24" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L24">
-        <v>4.5</v>
+        <v>179</v>
       </c>
       <c r="M24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -1819,34 +1828,31 @@
         <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F25">
-        <v>3039.9</v>
-      </c>
-      <c r="G25" t="s">
-        <v>110</v>
+        <v>38000</v>
       </c>
       <c r="H25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J25" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L25">
-        <v>3039.9</v>
+        <v>38</v>
       </c>
       <c r="M25" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="N25" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -1863,34 +1869,31 @@
         <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26">
-        <v>726.071</v>
-      </c>
-      <c r="G26" t="s">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="H26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L26">
-        <v>726.071</v>
+        <v>192</v>
       </c>
       <c r="M26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
@@ -1907,34 +1910,31 @@
         <v>74</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F27">
-        <v>1932.222</v>
-      </c>
-      <c r="G27" t="s">
-        <v>110</v>
-      </c>
-      <c r="I27" t="s">
-        <v>122</v>
+        <v>2724</v>
+      </c>
+      <c r="H27" t="s">
+        <v>118</v>
       </c>
       <c r="J27" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L27">
-        <v>1932.222</v>
+        <v>2724</v>
       </c>
       <c r="M27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
@@ -1951,31 +1951,31 @@
         <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F28">
-        <v>200.2</v>
+        <v>55</v>
       </c>
       <c r="H28" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J28" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K28" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L28">
-        <v>200.2</v>
+        <v>55</v>
       </c>
       <c r="M28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
@@ -1992,31 +1992,31 @@
         <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F29">
-        <v>57.2</v>
+        <v>583</v>
       </c>
       <c r="H29" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J29" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L29">
-        <v>68.068</v>
+        <v>583</v>
       </c>
       <c r="M29" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O29" t="b">
         <v>0</v>
@@ -2033,13 +2033,13 @@
         <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F30">
-        <v>2.255</v>
+        <v>12578</v>
       </c>
       <c r="I30" t="s">
         <v>122</v>
@@ -2051,13 +2051,13 @@
         <v>131</v>
       </c>
       <c r="L30">
-        <v>2.68345</v>
+        <v>12578</v>
       </c>
       <c r="M30" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O30" t="b">
         <v>0</v>
@@ -2074,16 +2074,19 @@
         <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F31">
-        <v>2229</v>
-      </c>
-      <c r="H31" t="s">
-        <v>114</v>
+        <v>1932.222</v>
+      </c>
+      <c r="G31" t="s">
+        <v>110</v>
+      </c>
+      <c r="I31" t="s">
+        <v>122</v>
       </c>
       <c r="J31" t="s">
         <v>125</v>
@@ -2092,13 +2095,13 @@
         <v>131</v>
       </c>
       <c r="L31">
-        <v>2229</v>
+        <v>1932.222</v>
       </c>
       <c r="M31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
@@ -2115,16 +2118,16 @@
         <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F32">
-        <v>924.081</v>
-      </c>
-      <c r="H32" t="s">
-        <v>115</v>
+        <v>2.255</v>
+      </c>
+      <c r="I32" t="s">
+        <v>122</v>
       </c>
       <c r="J32" t="s">
         <v>125</v>
@@ -2133,13 +2136,13 @@
         <v>131</v>
       </c>
       <c r="L32">
-        <v>924.081</v>
+        <v>2.68345</v>
       </c>
       <c r="M32" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N32" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
@@ -2156,31 +2159,31 @@
         <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F33">
-        <v>2724</v>
-      </c>
-      <c r="H33" t="s">
-        <v>111</v>
+        <v>4346.921</v>
+      </c>
+      <c r="I33" t="s">
+        <v>122</v>
       </c>
       <c r="J33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L33">
-        <v>2724</v>
+        <v>4346.921</v>
       </c>
       <c r="M33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
@@ -2197,13 +2200,13 @@
         <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F34">
-        <v>4346.921</v>
+        <v>619.366</v>
       </c>
       <c r="I34" t="s">
         <v>122</v>
@@ -2215,13 +2218,13 @@
         <v>131</v>
       </c>
       <c r="L34">
-        <v>4346.921</v>
+        <v>545.0420799999999</v>
       </c>
       <c r="M34" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N34" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
@@ -2238,31 +2241,31 @@
         <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F35">
-        <v>6390.4</v>
-      </c>
-      <c r="H35" t="s">
-        <v>112</v>
+        <v>175</v>
+      </c>
+      <c r="I35" t="s">
+        <v>122</v>
       </c>
       <c r="J35" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K35" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L35">
-        <v>6390.4</v>
+        <v>0.26425</v>
       </c>
       <c r="M35" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N35" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
@@ -2279,31 +2282,31 @@
         <v>74</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F36">
-        <v>5069.3</v>
-      </c>
-      <c r="H36" t="s">
-        <v>113</v>
+        <v>734.521</v>
+      </c>
+      <c r="I36" t="s">
+        <v>122</v>
       </c>
       <c r="J36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L36">
-        <v>5069.3</v>
+        <v>734.521</v>
       </c>
       <c r="M36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
@@ -2320,16 +2323,16 @@
         <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F37">
-        <v>380.687</v>
-      </c>
-      <c r="H37" t="s">
-        <v>114</v>
+        <v>5</v>
+      </c>
+      <c r="I37" t="s">
+        <v>122</v>
       </c>
       <c r="J37" t="s">
         <v>125</v>
@@ -2338,13 +2341,13 @@
         <v>131</v>
       </c>
       <c r="L37">
-        <v>335.00456</v>
+        <v>0.009200000000000002</v>
       </c>
       <c r="M37" t="s">
         <v>136</v>
       </c>
       <c r="N37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
@@ -2361,16 +2364,16 @@
         <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F38">
-        <v>336.521</v>
-      </c>
-      <c r="H38" t="s">
-        <v>115</v>
+        <v>626.983579787717</v>
+      </c>
+      <c r="I38" t="s">
+        <v>122</v>
       </c>
       <c r="J38" t="s">
         <v>125</v>
@@ -2379,13 +2382,13 @@
         <v>131</v>
       </c>
       <c r="L38">
-        <v>296.13848</v>
+        <v>626.983579787717</v>
       </c>
       <c r="M38" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N38" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
@@ -2402,31 +2405,31 @@
         <v>74</v>
       </c>
       <c r="D39" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F39">
-        <v>619.366</v>
-      </c>
-      <c r="I39" t="s">
-        <v>122</v>
+        <v>5977.02</v>
+      </c>
+      <c r="H39" t="s">
+        <v>119</v>
       </c>
       <c r="J39" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L39">
-        <v>545.0420799999999</v>
+        <v>5977.02</v>
       </c>
       <c r="M39" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N39" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O39" t="b">
         <v>0</v>
@@ -2443,31 +2446,31 @@
         <v>74</v>
       </c>
       <c r="D40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F40">
-        <v>18.9</v>
+        <v>2819.39</v>
       </c>
       <c r="H40" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="J40" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K40" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L40">
-        <v>18.9</v>
+        <v>2819.39</v>
       </c>
       <c r="M40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
@@ -2484,31 +2487,31 @@
         <v>74</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F41">
-        <v>26575</v>
+        <v>231239.82</v>
       </c>
       <c r="H41" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J41" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K41" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L41">
-        <v>40.12825</v>
+        <v>231.23982</v>
       </c>
       <c r="M41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
@@ -2525,31 +2528,31 @@
         <v>74</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F42">
-        <v>175</v>
-      </c>
-      <c r="I42" t="s">
-        <v>122</v>
+        <v>526.21</v>
+      </c>
+      <c r="H42" t="s">
+        <v>119</v>
       </c>
       <c r="J42" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K42" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L42">
-        <v>0.26425</v>
+        <v>526.21</v>
       </c>
       <c r="M42" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N42" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
@@ -2566,31 +2569,31 @@
         <v>74</v>
       </c>
       <c r="D43" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F43">
-        <v>55</v>
+        <v>2269.57</v>
       </c>
       <c r="H43" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J43" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K43" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L43">
-        <v>55</v>
+        <v>2269.57</v>
       </c>
       <c r="M43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N43" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O43" t="b">
         <v>0</v>
@@ -2607,31 +2610,31 @@
         <v>74</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E44" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F44">
-        <v>583</v>
+        <v>149.1</v>
       </c>
       <c r="H44" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J44" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K44" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L44">
-        <v>583</v>
+        <v>149.1</v>
       </c>
       <c r="M44" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N44" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O44" t="b">
         <v>0</v>
@@ -2648,31 +2651,31 @@
         <v>74</v>
       </c>
       <c r="D45" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E45" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F45">
-        <v>838.8</v>
+        <v>6390.4</v>
       </c>
       <c r="H45" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J45" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L45">
-        <v>838.8</v>
+        <v>6390.4</v>
       </c>
       <c r="M45" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O45" t="b">
         <v>0</v>
@@ -2689,31 +2692,31 @@
         <v>74</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F46">
-        <v>390.003</v>
+        <v>35.4</v>
       </c>
       <c r="H46" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J46" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K46" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L46">
-        <v>390.003</v>
+        <v>35.4</v>
       </c>
       <c r="M46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N46" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O46" t="b">
         <v>0</v>
@@ -2730,31 +2733,31 @@
         <v>74</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F47">
-        <v>734.521</v>
-      </c>
-      <c r="I47" t="s">
-        <v>122</v>
+        <v>60.4</v>
+      </c>
+      <c r="H47" t="s">
+        <v>120</v>
       </c>
       <c r="J47" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K47" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L47">
-        <v>734.521</v>
+        <v>60.4</v>
       </c>
       <c r="M47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O47" t="b">
         <v>0</v>
@@ -2771,31 +2774,31 @@
         <v>74</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F48">
-        <v>539</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H48" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K48" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="L48">
-        <v>539</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="M48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O48" t="b">
         <v>0</v>
@@ -2815,28 +2818,28 @@
         <v>99</v>
       </c>
       <c r="E49" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F49">
-        <v>73.95999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="H49" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J49" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K49" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L49">
-        <v>0.1360864</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N49" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O49" t="b">
         <v>0</v>
@@ -2853,31 +2856,31 @@
         <v>74</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E50" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F50">
-        <v>5</v>
-      </c>
-      <c r="I50" t="s">
-        <v>122</v>
+        <v>399.3</v>
+      </c>
+      <c r="H50" t="s">
+        <v>120</v>
       </c>
       <c r="J50" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K50" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L50">
-        <v>0.009200000000000002</v>
+        <v>399.3</v>
       </c>
       <c r="M50" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N50" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O50" t="b">
         <v>0</v>
@@ -2894,34 +2897,34 @@
         <v>74</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="E51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F51">
-        <v>6543598</v>
+        <v>1483.4</v>
       </c>
       <c r="G51" t="s">
         <v>110</v>
       </c>
       <c r="H51" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L51">
-        <v>2968.123704016</v>
+        <v>1483.4</v>
       </c>
       <c r="M51" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="N51" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="O51" t="b">
         <v>0</v>
@@ -2938,34 +2941,31 @@
         <v>74</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E52" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F52">
-        <v>511210</v>
-      </c>
-      <c r="G52" t="s">
-        <v>110</v>
+        <v>46.2</v>
       </c>
       <c r="H52" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J52" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K52" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L52">
-        <v>231.88076632</v>
+        <v>46.2</v>
       </c>
       <c r="M52" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="N52" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="O52" t="b">
         <v>0</v>
@@ -2982,31 +2982,31 @@
         <v>74</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F53">
-        <v>241.250566996281</v>
+        <v>4.5</v>
       </c>
       <c r="H53" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J53" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K53" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L53">
-        <v>241.250566996281</v>
+        <v>4.5</v>
       </c>
       <c r="M53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N53" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O53" t="b">
         <v>0</v>
@@ -3026,28 +3026,28 @@
         <v>101</v>
       </c>
       <c r="E54" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F54">
-        <v>100.705343372947</v>
+        <v>200.2</v>
       </c>
       <c r="H54" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J54" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K54" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L54">
-        <v>100.705343372947</v>
+        <v>200.2</v>
       </c>
       <c r="M54" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N54" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O54" t="b">
         <v>0</v>
@@ -3064,31 +3064,31 @@
         <v>74</v>
       </c>
       <c r="D55" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="E55" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F55">
-        <v>626.983579787717</v>
-      </c>
-      <c r="I55" t="s">
-        <v>122</v>
+        <v>5069.3</v>
+      </c>
+      <c r="H55" t="s">
+        <v>120</v>
       </c>
       <c r="J55" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K55" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L55">
-        <v>626.983579787717</v>
+        <v>5069.3</v>
       </c>
       <c r="M55" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O55" t="b">
         <v>0</v>
@@ -3108,10 +3108,10 @@
         <v>102</v>
       </c>
       <c r="E56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F56">
-        <v>486.3</v>
+        <v>18.9</v>
       </c>
       <c r="H56" t="s">
         <v>120</v>
@@ -3123,13 +3123,13 @@
         <v>134</v>
       </c>
       <c r="L56">
-        <v>486.3</v>
+        <v>18.9</v>
       </c>
       <c r="M56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N56" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O56" t="b">
         <v>0</v>
@@ -3146,19 +3146,16 @@
         <v>74</v>
       </c>
       <c r="D57" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F57">
-        <v>2599.5</v>
-      </c>
-      <c r="G57" t="s">
-        <v>110</v>
+        <v>539</v>
       </c>
       <c r="H57" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J57" t="s">
         <v>128</v>
@@ -3167,13 +3164,13 @@
         <v>134</v>
       </c>
       <c r="L57">
-        <v>2599.5</v>
+        <v>539</v>
       </c>
       <c r="M57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O57" t="b">
         <v>0</v>
@@ -3190,13 +3187,13 @@
         <v>74</v>
       </c>
       <c r="D58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E58" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F58">
-        <v>245</v>
+        <v>8.1</v>
       </c>
       <c r="H58" t="s">
         <v>120</v>
@@ -3208,13 +3205,13 @@
         <v>134</v>
       </c>
       <c r="L58">
-        <v>245</v>
+        <v>8.1</v>
       </c>
       <c r="M58" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N58" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O58" t="b">
         <v>0</v>
@@ -3231,31 +3228,34 @@
         <v>74</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E59" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F59">
-        <v>1955.7</v>
+        <v>2599.5</v>
+      </c>
+      <c r="G59" t="s">
+        <v>110</v>
       </c>
       <c r="H59" t="s">
         <v>121</v>
       </c>
       <c r="J59" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K59" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L59">
-        <v>1955.7</v>
+        <v>2599.5</v>
       </c>
       <c r="M59" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N59" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O59" t="b">
         <v>0</v>
@@ -3272,31 +3272,31 @@
         <v>74</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F60">
-        <v>8.1</v>
+        <v>1955.7</v>
       </c>
       <c r="H60" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="J60" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K60" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L60">
-        <v>8.1</v>
+        <v>1955.7</v>
       </c>
       <c r="M60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N60" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O60" t="b">
         <v>0</v>

--- a/data/MetalliCan/pre_cleaned_data/material_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/material_df.xlsx
@@ -61,90 +61,156 @@
     <t>needs_density</t>
   </si>
   <si>
+    <t>TECH-aa76f6f2-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-12.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-11.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-7607a50e-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-7607a50e-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-cb85213a-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-11.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-13.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-15.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-11.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-13.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-15.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-16.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-19.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-20.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-12.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-13.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-9de9bb0d-2023.0-4.0</t>
+  </si>
+  <si>
     <t>TECH-b86f7d07-2023.0-5.0</t>
   </si>
   <si>
-    <t>TECH-cb85213a-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-7.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-8.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-9.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-10.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-12.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-13.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-14.0</t>
-  </si>
-  <si>
-    <t>TECH-687b8c8d-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-687b8c8d-2023.0-7.0</t>
-  </si>
-  <si>
     <t>TECH-44857446-2023.0-5.0</t>
   </si>
   <si>
-    <t>TECH-9de9bb0d-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-8.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-9.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-10.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-11.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-13.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-15.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-8.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-10.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-12.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-14.0</t>
-  </si>
-  <si>
     <t>TECH-GRP-0d911886-2023.0-2.0</t>
   </si>
   <si>
@@ -172,283 +238,217 @@
     <t>TECH-GRP-0d911886-2023.0-16.0</t>
   </si>
   <si>
-    <t>TECH-0aadf28f-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023.0-9.0</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023.0-11.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-10.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-11.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-13.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-14.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-15.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-16.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-19.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-20.0</t>
-  </si>
-  <si>
-    <t>TECH-7607a50e-2023.0-7.0</t>
-  </si>
-  <si>
-    <t>TECH-7607a50e-2023.0-8.0</t>
-  </si>
-  <si>
     <t>Material use</t>
   </si>
   <si>
+    <t>2'' balls</t>
+  </si>
+  <si>
+    <t>3/4'' balls</t>
+  </si>
+  <si>
+    <t>Anti-scalant</t>
+  </si>
+  <si>
+    <t>Flocculant</t>
+  </si>
+  <si>
+    <t>Lime</t>
+  </si>
+  <si>
+    <t>Polyfroth h57</t>
+  </si>
+  <si>
+    <t>S60 SAG Balls</t>
+  </si>
+  <si>
+    <t>2.5'' balls</t>
+  </si>
+  <si>
+    <t>5.5'' balls</t>
+  </si>
+  <si>
+    <t>Caustic soda</t>
+  </si>
+  <si>
+    <t>Cyanide</t>
+  </si>
+  <si>
+    <t>Total blasting agents used e.g. ANFO</t>
+  </si>
+  <si>
+    <t>Total sodium cyanide used</t>
+  </si>
+  <si>
+    <t>Explosives</t>
+  </si>
+  <si>
+    <t>Cement</t>
+  </si>
+  <si>
+    <t>Grinding media</t>
+  </si>
+  <si>
+    <t>Hydrochloric acid (HCL)</t>
+  </si>
+  <si>
+    <t>Lubricants</t>
+  </si>
+  <si>
+    <t>Sodium cyanide (NaCN)</t>
+  </si>
+  <si>
+    <t>Tires</t>
+  </si>
+  <si>
+    <t>Carbon</t>
+  </si>
+  <si>
+    <t>Compressor oil</t>
+  </si>
+  <si>
+    <t>Grease</t>
+  </si>
+  <si>
+    <t>Hydraulic oil</t>
+  </si>
+  <si>
+    <t>Motor/drill oil</t>
+  </si>
+  <si>
+    <t>Sulfur dioxide</t>
+  </si>
+  <si>
+    <t>Transmission oil</t>
+  </si>
+  <si>
+    <t>Nitric acid (HNO3)</t>
+  </si>
+  <si>
+    <t>Sulfuric acid (H2SO4)</t>
+  </si>
+  <si>
     <t>Surface/underground emulsion &amp; ANFO</t>
   </si>
   <si>
-    <t>Explosives</t>
-  </si>
-  <si>
-    <t>Cement</t>
-  </si>
-  <si>
-    <t>Grinding media</t>
-  </si>
-  <si>
-    <t>Lime</t>
-  </si>
-  <si>
-    <t>Lubricants</t>
-  </si>
-  <si>
-    <t>Nitric acid (HNO3)</t>
-  </si>
-  <si>
-    <t>Sodium cyanide (NaCN)</t>
-  </si>
-  <si>
-    <t>Sulfuric acid (H2SO4)</t>
-  </si>
-  <si>
-    <t>Tires</t>
-  </si>
-  <si>
-    <t>Total blasting agents used e.g. ANFO</t>
-  </si>
-  <si>
-    <t>Total sodium cyanide used</t>
-  </si>
-  <si>
-    <t>Hydrochloric acid (HCL)</t>
-  </si>
-  <si>
-    <t>2'' balls</t>
-  </si>
-  <si>
-    <t>3/4'' balls</t>
-  </si>
-  <si>
-    <t>Anti-scalant</t>
-  </si>
-  <si>
-    <t>Flocculant</t>
-  </si>
-  <si>
-    <t>Polyfroth h57</t>
-  </si>
-  <si>
-    <t>S60 SAG Balls</t>
-  </si>
-  <si>
-    <t>2.5'' balls</t>
-  </si>
-  <si>
-    <t>5.5'' balls</t>
-  </si>
-  <si>
-    <t>Caustic soda</t>
-  </si>
-  <si>
-    <t>Cyanide</t>
-  </si>
-  <si>
-    <t>Carbon</t>
-  </si>
-  <si>
-    <t>Compressor oil</t>
-  </si>
-  <si>
-    <t>Grease</t>
-  </si>
-  <si>
-    <t>Hydraulic oil</t>
-  </si>
-  <si>
-    <t>Motor/drill oil</t>
-  </si>
-  <si>
-    <t>Sulfur dioxide</t>
-  </si>
-  <si>
-    <t>Transmission oil</t>
+    <t>t</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>kl</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
   <si>
     <t>pounds</t>
   </si>
   <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>kl</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
     <t>Explosives, treated as material input because in t</t>
   </si>
   <si>
+    <t>BC-MAIN-aa76f6f2</t>
+  </si>
+  <si>
+    <t>ON-MAIN-0aadf28f</t>
+  </si>
+  <si>
+    <t>ON-MAIN-687b8c8d</t>
+  </si>
+  <si>
+    <t>ON-MAIN-7607a50e</t>
+  </si>
+  <si>
+    <t>ON-MAIN-cb85213a</t>
+  </si>
+  <si>
+    <t>ON-MAIN-fefeaee4</t>
+  </si>
+  <si>
+    <t>QC-MAIN-02884fb5</t>
+  </si>
+  <si>
+    <t>QC-MAIN-6dc537e6</t>
+  </si>
+  <si>
+    <t>QC-MAIN-9de9bb0d</t>
+  </si>
+  <si>
     <t>QC-MAIN-b86f7d07</t>
   </si>
   <si>
-    <t>ON-MAIN-cb85213a</t>
-  </si>
-  <si>
-    <t>QC-MAIN-6dc537e6</t>
-  </si>
-  <si>
-    <t>ON-MAIN-687b8c8d</t>
-  </si>
-  <si>
     <t>YT-MAIN-44857446</t>
   </si>
   <si>
-    <t>QC-MAIN-9de9bb0d</t>
-  </si>
-  <si>
-    <t>ON-MAIN-fefeaee4</t>
-  </si>
-  <si>
-    <t>BC-MAIN-aa76f6f2</t>
-  </si>
-  <si>
-    <t>ON-MAIN-0aadf28f</t>
-  </si>
-  <si>
-    <t>QC-MAIN-02884fb5</t>
-  </si>
-  <si>
-    <t>ON-MAIN-7607a50e</t>
-  </si>
-  <si>
     <t>GRP-0d911886</t>
   </si>
   <si>
+    <t>CMP-d94be190</t>
+  </si>
+  <si>
+    <t>CMP-3a4ccc7f</t>
+  </si>
+  <si>
+    <t>CMP-3d2c4955</t>
+  </si>
+  <si>
+    <t>CMP-4a434d72</t>
+  </si>
+  <si>
+    <t>CMP-3d0a95b7</t>
+  </si>
+  <si>
     <t>CMP-7e360a1f</t>
   </si>
   <si>
-    <t>CMP-3d2c4955</t>
-  </si>
-  <si>
-    <t>CMP-4a434d72</t>
-  </si>
-  <si>
-    <t>CMP-3a4ccc7f</t>
-  </si>
-  <si>
-    <t>CMP-d94be190</t>
-  </si>
-  <si>
-    <t>CMP-3d0a95b7</t>
+    <t>NewGoldInc_2023-New-Gold-ESG-Data-Factbook</t>
+  </si>
+  <si>
+    <t>AlamosGoldInc_Data_2023</t>
+  </si>
+  <si>
+    <t>WesdomeGoldMinesLtd._ESG_data_2023</t>
+  </si>
+  <si>
+    <t>NewmontCorporation_Newmont-2023-Performance-Data-Tables-V4-locked</t>
+  </si>
+  <si>
+    <t>IAMGOLDCorporation_2023_iamgold-esg-performance-data-final_protected</t>
   </si>
   <si>
     <t>HeclaMiningCompany_SR_2023</t>
   </si>
   <si>
-    <t>WesdomeGoldMinesLtd._ESG_data_2023</t>
-  </si>
-  <si>
-    <t>NewmontCorporation_Newmont-2023-Performance-Data-Tables-V4-locked</t>
-  </si>
-  <si>
-    <t>AlamosGoldInc_Data_2023</t>
-  </si>
-  <si>
-    <t>NewGoldInc_2023-New-Gold-ESG-Data-Factbook</t>
-  </si>
-  <si>
-    <t>IAMGOLDCorporation_2023_iamgold-esg-performance-data-final_protected</t>
+    <t>kg→t</t>
+  </si>
+  <si>
+    <t>L×density→t</t>
   </si>
   <si>
     <t>lbs→t</t>
   </si>
   <si>
-    <t>L×density→t</t>
-  </si>
-  <si>
-    <t>kg→t</t>
+    <t>reported in tonnes</t>
+  </si>
+  <si>
+    <t>kg/1000</t>
+  </si>
+  <si>
+    <t>kl×density=1.19 kg/L</t>
+  </si>
+  <si>
+    <t>kl×density=0.88 kg/L</t>
+  </si>
+  <si>
+    <t>l×density=1.51 kg/L</t>
+  </si>
+  <si>
+    <t>l×density=1.84 kg/L</t>
   </si>
   <si>
     <t>lbs×0.453592/1000</t>
-  </si>
-  <si>
-    <t>reported in tonnes</t>
-  </si>
-  <si>
-    <t>kl×density=0.88 kg/L</t>
-  </si>
-  <si>
-    <t>l×density=1.51 kg/L</t>
-  </si>
-  <si>
-    <t>l×density=1.84 kg/L</t>
-  </si>
-  <si>
-    <t>kl×density=1.19 kg/L</t>
-  </si>
-  <si>
-    <t>kg/1000</t>
   </si>
 </sst>
 </file>
@@ -873,10 +873,7 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>6543598</v>
-      </c>
-      <c r="G2" t="s">
-        <v>110</v>
+        <v>980</v>
       </c>
       <c r="H2" t="s">
         <v>111</v>
@@ -888,10 +885,10 @@
         <v>129</v>
       </c>
       <c r="L2">
-        <v>2968.123704016</v>
+        <v>980</v>
       </c>
       <c r="M2" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="N2" t="s">
         <v>138</v>
@@ -914,31 +911,28 @@
         <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F3">
-        <v>1211</v>
-      </c>
-      <c r="G3" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="H3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L3">
-        <v>1211</v>
+        <v>179</v>
       </c>
       <c r="M3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -961,22 +955,22 @@
         <v>106</v>
       </c>
       <c r="F4">
-        <v>27374</v>
+        <v>38000</v>
       </c>
       <c r="H4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L4">
-        <v>27374</v>
+        <v>38</v>
       </c>
       <c r="M4" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="N4" t="s">
         <v>139</v>
@@ -999,31 +993,28 @@
         <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F5">
-        <v>3039.9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="H5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L5">
-        <v>3039.9</v>
+        <v>192</v>
       </c>
       <c r="M5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
@@ -1043,28 +1034,28 @@
         <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F6">
-        <v>2229</v>
+        <v>2724</v>
       </c>
       <c r="H6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L6">
-        <v>2229</v>
+        <v>2724</v>
       </c>
       <c r="M6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -1084,28 +1075,28 @@
         <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F7">
-        <v>380.687</v>
+        <v>55</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L7">
-        <v>335.00456</v>
+        <v>55</v>
       </c>
       <c r="M7" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="N7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
@@ -1125,28 +1116,28 @@
         <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F8">
-        <v>26575</v>
+        <v>583</v>
       </c>
       <c r="H8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L8">
-        <v>40.12825</v>
+        <v>583</v>
       </c>
       <c r="M8" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="N8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -1166,28 +1157,28 @@
         <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F9">
-        <v>838.8</v>
+        <v>5977.02</v>
       </c>
       <c r="H9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L9">
-        <v>838.8</v>
+        <v>5977.02</v>
       </c>
       <c r="M9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -1207,28 +1198,28 @@
         <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F10">
-        <v>73.95999999999999</v>
+        <v>2819.39</v>
       </c>
       <c r="H10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L10">
-        <v>0.1360864</v>
+        <v>2819.39</v>
       </c>
       <c r="M10" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="N10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
@@ -1245,28 +1236,28 @@
         <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
         <v>106</v>
       </c>
       <c r="F11">
-        <v>241.250566996281</v>
+        <v>231239.82</v>
       </c>
       <c r="H11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L11">
-        <v>241.250566996281</v>
+        <v>231.23982</v>
       </c>
       <c r="M11" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="N11" t="s">
         <v>139</v>
@@ -1286,31 +1277,31 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F12">
-        <v>486.3</v>
+        <v>526.21</v>
       </c>
       <c r="H12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L12">
-        <v>486.3</v>
+        <v>526.21</v>
       </c>
       <c r="M12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -1327,31 +1318,31 @@
         <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F13">
-        <v>245</v>
+        <v>2269.57</v>
       </c>
       <c r="H13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K13" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L13">
-        <v>245</v>
+        <v>2269.57</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -1368,19 +1359,16 @@
         <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
         <v>105</v>
       </c>
       <c r="F14">
-        <v>511210</v>
-      </c>
-      <c r="G14" t="s">
-        <v>110</v>
+        <v>149.1</v>
       </c>
       <c r="H14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J14" t="s">
         <v>123</v>
@@ -1389,10 +1377,10 @@
         <v>129</v>
       </c>
       <c r="L14">
-        <v>231.88076632</v>
+        <v>149.1</v>
       </c>
       <c r="M14" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="N14" t="s">
         <v>138</v>
@@ -1412,34 +1400,31 @@
         <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F15">
-        <v>506</v>
-      </c>
-      <c r="G15" t="s">
-        <v>110</v>
+        <v>6390.4</v>
       </c>
       <c r="H15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L15">
-        <v>506</v>
+        <v>6390.4</v>
       </c>
       <c r="M15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
@@ -1456,31 +1441,31 @@
         <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F16">
-        <v>9417.6</v>
+        <v>486.3</v>
       </c>
       <c r="H16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L16">
-        <v>9417.6</v>
+        <v>486.3</v>
       </c>
       <c r="M16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -1497,34 +1482,31 @@
         <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F17">
-        <v>726.071</v>
-      </c>
-      <c r="G17" t="s">
-        <v>110</v>
+        <v>245</v>
       </c>
       <c r="H17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L17">
-        <v>726.071</v>
+        <v>245</v>
       </c>
       <c r="M17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -1541,31 +1523,34 @@
         <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F18">
-        <v>57.2</v>
+        <v>2599.5</v>
+      </c>
+      <c r="G18" t="s">
+        <v>110</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L18">
-        <v>68.068</v>
+        <v>2599.5</v>
       </c>
       <c r="M18" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="N18" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -1582,31 +1567,31 @@
         <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F19">
-        <v>924.081</v>
+        <v>1955.7</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L19">
-        <v>924.081</v>
+        <v>1955.7</v>
       </c>
       <c r="M19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -1623,16 +1608,19 @@
         <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F20">
-        <v>336.521</v>
+        <v>1211</v>
+      </c>
+      <c r="G20" t="s">
+        <v>110</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J20" t="s">
         <v>125</v>
@@ -1641,13 +1629,13 @@
         <v>131</v>
       </c>
       <c r="L20">
-        <v>296.13848</v>
+        <v>1211</v>
       </c>
       <c r="M20" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="N20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -1664,31 +1652,31 @@
         <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F21">
-        <v>390.003</v>
+        <v>9417.6</v>
       </c>
       <c r="H21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L21">
-        <v>390.003</v>
+        <v>9417.6</v>
       </c>
       <c r="M21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -1705,31 +1693,34 @@
         <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F22">
-        <v>100.705343372947</v>
+        <v>726.071</v>
+      </c>
+      <c r="G22" t="s">
+        <v>110</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L22">
-        <v>100.705343372947</v>
+        <v>726.071</v>
       </c>
       <c r="M22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -1746,31 +1737,31 @@
         <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F23">
-        <v>980</v>
+        <v>57.2</v>
       </c>
       <c r="H23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L23">
-        <v>980</v>
+        <v>68.068</v>
       </c>
       <c r="M23" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="N23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -1787,31 +1778,31 @@
         <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F24">
-        <v>179</v>
+        <v>924.081</v>
       </c>
       <c r="H24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L24">
-        <v>179</v>
+        <v>924.081</v>
       </c>
       <c r="M24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -1828,31 +1819,31 @@
         <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F25">
-        <v>38000</v>
+        <v>336.521</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L25">
-        <v>38</v>
+        <v>296.13848</v>
       </c>
       <c r="M25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N25" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -1869,31 +1860,31 @@
         <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F26">
-        <v>192</v>
+        <v>390.003</v>
       </c>
       <c r="H26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L26">
-        <v>192</v>
+        <v>390.003</v>
       </c>
       <c r="M26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
@@ -1910,31 +1901,31 @@
         <v>74</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F27">
-        <v>2724</v>
+        <v>100.7053434</v>
       </c>
       <c r="H27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L27">
-        <v>2724</v>
+        <v>100.7053434</v>
       </c>
       <c r="M27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
@@ -1951,16 +1942,16 @@
         <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F28">
-        <v>55</v>
+        <v>35.4</v>
       </c>
       <c r="H28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J28" t="s">
         <v>127</v>
@@ -1969,13 +1960,13 @@
         <v>133</v>
       </c>
       <c r="L28">
-        <v>55</v>
+        <v>35.4</v>
       </c>
       <c r="M28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
@@ -1992,16 +1983,16 @@
         <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F29">
-        <v>583</v>
+        <v>60.4</v>
       </c>
       <c r="H29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J29" t="s">
         <v>127</v>
@@ -2010,13 +2001,13 @@
         <v>133</v>
       </c>
       <c r="L29">
-        <v>583</v>
+        <v>60.4</v>
       </c>
       <c r="M29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O29" t="b">
         <v>0</v>
@@ -2033,31 +2024,31 @@
         <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F30">
-        <v>12578</v>
-      </c>
-      <c r="I30" t="s">
-        <v>122</v>
+        <v>86.59999999999999</v>
+      </c>
+      <c r="H30" t="s">
+        <v>117</v>
       </c>
       <c r="J30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K30" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L30">
-        <v>12578</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="M30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O30" t="b">
         <v>0</v>
@@ -2074,34 +2065,31 @@
         <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F31">
-        <v>1932.222</v>
-      </c>
-      <c r="G31" t="s">
-        <v>110</v>
-      </c>
-      <c r="I31" t="s">
-        <v>122</v>
+        <v>1.5</v>
+      </c>
+      <c r="H31" t="s">
+        <v>117</v>
       </c>
       <c r="J31" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L31">
-        <v>1932.222</v>
+        <v>1.5</v>
       </c>
       <c r="M31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
@@ -2118,31 +2106,31 @@
         <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F32">
-        <v>2.255</v>
-      </c>
-      <c r="I32" t="s">
-        <v>122</v>
+        <v>399.3</v>
+      </c>
+      <c r="H32" t="s">
+        <v>117</v>
       </c>
       <c r="J32" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K32" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L32">
-        <v>2.68345</v>
+        <v>399.3</v>
       </c>
       <c r="M32" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="N32" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
@@ -2159,31 +2147,34 @@
         <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F33">
-        <v>4346.921</v>
-      </c>
-      <c r="I33" t="s">
-        <v>122</v>
+        <v>1483.4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>110</v>
+      </c>
+      <c r="H33" t="s">
+        <v>117</v>
       </c>
       <c r="J33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L33">
-        <v>4346.921</v>
+        <v>1483.4</v>
       </c>
       <c r="M33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
@@ -2200,31 +2191,31 @@
         <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F34">
-        <v>619.366</v>
-      </c>
-      <c r="I34" t="s">
-        <v>122</v>
+        <v>46.2</v>
+      </c>
+      <c r="H34" t="s">
+        <v>117</v>
       </c>
       <c r="J34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K34" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L34">
-        <v>545.0420799999999</v>
+        <v>46.2</v>
       </c>
       <c r="M34" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="N34" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
@@ -2241,31 +2232,31 @@
         <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F35">
-        <v>175</v>
-      </c>
-      <c r="I35" t="s">
-        <v>122</v>
+        <v>4.5</v>
+      </c>
+      <c r="H35" t="s">
+        <v>117</v>
       </c>
       <c r="J35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K35" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L35">
-        <v>0.26425</v>
+        <v>4.5</v>
       </c>
       <c r="M35" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="N35" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
@@ -2282,31 +2273,31 @@
         <v>74</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F36">
-        <v>734.521</v>
-      </c>
-      <c r="I36" t="s">
-        <v>122</v>
+        <v>200.2</v>
+      </c>
+      <c r="H36" t="s">
+        <v>117</v>
       </c>
       <c r="J36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L36">
-        <v>734.521</v>
+        <v>200.2</v>
       </c>
       <c r="M36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
@@ -2323,31 +2314,31 @@
         <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E37" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F37">
-        <v>5</v>
-      </c>
-      <c r="I37" t="s">
-        <v>122</v>
+        <v>5069.3</v>
+      </c>
+      <c r="H37" t="s">
+        <v>117</v>
       </c>
       <c r="J37" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K37" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L37">
-        <v>0.009200000000000002</v>
+        <v>5069.3</v>
       </c>
       <c r="M37" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="N37" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
@@ -2364,31 +2355,31 @@
         <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="E38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F38">
-        <v>626.983579787717</v>
-      </c>
-      <c r="I38" t="s">
-        <v>122</v>
+        <v>18.9</v>
+      </c>
+      <c r="H38" t="s">
+        <v>117</v>
       </c>
       <c r="J38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L38">
-        <v>626.983579787717</v>
+        <v>18.9</v>
       </c>
       <c r="M38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
@@ -2405,16 +2396,16 @@
         <v>74</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F39">
-        <v>5977.02</v>
+        <v>539</v>
       </c>
       <c r="H39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J39" t="s">
         <v>127</v>
@@ -2423,13 +2414,13 @@
         <v>133</v>
       </c>
       <c r="L39">
-        <v>5977.02</v>
+        <v>539</v>
       </c>
       <c r="M39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O39" t="b">
         <v>0</v>
@@ -2446,16 +2437,16 @@
         <v>74</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F40">
-        <v>2819.39</v>
+        <v>8.1</v>
       </c>
       <c r="H40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J40" t="s">
         <v>127</v>
@@ -2464,13 +2455,13 @@
         <v>133</v>
       </c>
       <c r="L40">
-        <v>2819.39</v>
+        <v>8.1</v>
       </c>
       <c r="M40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
@@ -2487,31 +2478,31 @@
         <v>74</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E41" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F41">
-        <v>231239.82</v>
+        <v>27374</v>
       </c>
       <c r="H41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L41">
-        <v>231.23982</v>
+        <v>27374</v>
       </c>
       <c r="M41" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="N41" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
@@ -2528,31 +2519,34 @@
         <v>74</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F42">
-        <v>526.21</v>
+        <v>3039.9</v>
+      </c>
+      <c r="G42" t="s">
+        <v>110</v>
       </c>
       <c r="H42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K42" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L42">
-        <v>526.21</v>
+        <v>3039.9</v>
       </c>
       <c r="M42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
@@ -2569,31 +2563,31 @@
         <v>74</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F43">
-        <v>2269.57</v>
+        <v>2229</v>
       </c>
       <c r="H43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K43" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L43">
-        <v>2269.57</v>
+        <v>2229</v>
       </c>
       <c r="M43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O43" t="b">
         <v>0</v>
@@ -2610,31 +2604,31 @@
         <v>74</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E44" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F44">
-        <v>149.1</v>
+        <v>380.687</v>
       </c>
       <c r="H44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L44">
-        <v>149.1</v>
+        <v>335.00456</v>
       </c>
       <c r="M44" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="N44" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O44" t="b">
         <v>0</v>
@@ -2651,31 +2645,31 @@
         <v>74</v>
       </c>
       <c r="D45" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="E45" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F45">
-        <v>6390.4</v>
+        <v>26575</v>
       </c>
       <c r="H45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J45" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L45">
-        <v>6390.4</v>
+        <v>40.12825</v>
       </c>
       <c r="M45" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="N45" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="O45" t="b">
         <v>0</v>
@@ -2692,31 +2686,31 @@
         <v>74</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F46">
-        <v>35.4</v>
+        <v>838.8</v>
       </c>
       <c r="H46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J46" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K46" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L46">
-        <v>35.4</v>
+        <v>838.8</v>
       </c>
       <c r="M46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O46" t="b">
         <v>0</v>
@@ -2733,31 +2727,31 @@
         <v>74</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E47" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F47">
-        <v>60.4</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="H47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L47">
-        <v>60.4</v>
+        <v>0.1360864</v>
       </c>
       <c r="M47" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="N47" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="O47" t="b">
         <v>0</v>
@@ -2774,31 +2768,31 @@
         <v>74</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F48">
-        <v>86.59999999999999</v>
+        <v>241.250567</v>
       </c>
       <c r="H48" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J48" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K48" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L48">
-        <v>86.59999999999999</v>
+        <v>241.250567</v>
       </c>
       <c r="M48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O48" t="b">
         <v>0</v>
@@ -2815,31 +2809,34 @@
         <v>74</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F49">
-        <v>1.5</v>
+        <v>506</v>
+      </c>
+      <c r="G49" t="s">
+        <v>110</v>
       </c>
       <c r="H49" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J49" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K49" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L49">
-        <v>1.5</v>
+        <v>506</v>
       </c>
       <c r="M49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O49" t="b">
         <v>0</v>
@@ -2856,13 +2853,16 @@
         <v>74</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E50" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F50">
-        <v>399.3</v>
+        <v>6543598</v>
+      </c>
+      <c r="G50" t="s">
+        <v>110</v>
       </c>
       <c r="H50" t="s">
         <v>120</v>
@@ -2874,13 +2874,13 @@
         <v>134</v>
       </c>
       <c r="L50">
-        <v>399.3</v>
+        <v>2968.123704016</v>
       </c>
       <c r="M50" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="N50" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="O50" t="b">
         <v>0</v>
@@ -2897,19 +2897,19 @@
         <v>74</v>
       </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="E51" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F51">
-        <v>1483.4</v>
+        <v>511210</v>
       </c>
       <c r="G51" t="s">
         <v>110</v>
       </c>
       <c r="H51" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J51" t="s">
         <v>128</v>
@@ -2918,13 +2918,13 @@
         <v>134</v>
       </c>
       <c r="L51">
-        <v>1483.4</v>
+        <v>231.88076632</v>
       </c>
       <c r="M51" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="N51" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="O51" t="b">
         <v>0</v>
@@ -2941,31 +2941,31 @@
         <v>74</v>
       </c>
       <c r="D52" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E52" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F52">
-        <v>46.2</v>
-      </c>
-      <c r="H52" t="s">
-        <v>120</v>
+        <v>12578</v>
+      </c>
+      <c r="I52" t="s">
+        <v>122</v>
       </c>
       <c r="J52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K52" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L52">
-        <v>46.2</v>
+        <v>12578</v>
       </c>
       <c r="M52" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N52" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O52" t="b">
         <v>0</v>
@@ -2982,31 +2982,34 @@
         <v>74</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E53" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F53">
-        <v>4.5</v>
-      </c>
-      <c r="H53" t="s">
-        <v>120</v>
+        <v>1932.222</v>
+      </c>
+      <c r="G53" t="s">
+        <v>110</v>
+      </c>
+      <c r="I53" t="s">
+        <v>122</v>
       </c>
       <c r="J53" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K53" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L53">
-        <v>4.5</v>
+        <v>1932.222</v>
       </c>
       <c r="M53" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O53" t="b">
         <v>0</v>
@@ -3023,31 +3026,31 @@
         <v>74</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E54" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F54">
-        <v>200.2</v>
-      </c>
-      <c r="H54" t="s">
-        <v>120</v>
+        <v>2.255</v>
+      </c>
+      <c r="I54" t="s">
+        <v>122</v>
       </c>
       <c r="J54" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K54" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L54">
-        <v>200.2</v>
+        <v>2.68345</v>
       </c>
       <c r="M54" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="N54" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O54" t="b">
         <v>0</v>
@@ -3067,28 +3070,28 @@
         <v>79</v>
       </c>
       <c r="E55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F55">
-        <v>5069.3</v>
-      </c>
-      <c r="H55" t="s">
-        <v>120</v>
+        <v>4346.921</v>
+      </c>
+      <c r="I55" t="s">
+        <v>122</v>
       </c>
       <c r="J55" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K55" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L55">
-        <v>5069.3</v>
+        <v>4346.921</v>
       </c>
       <c r="M55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O55" t="b">
         <v>0</v>
@@ -3105,31 +3108,31 @@
         <v>74</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F56">
-        <v>18.9</v>
-      </c>
-      <c r="H56" t="s">
-        <v>120</v>
+        <v>619.366</v>
+      </c>
+      <c r="I56" t="s">
+        <v>122</v>
       </c>
       <c r="J56" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K56" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L56">
-        <v>18.9</v>
+        <v>545.0420799999999</v>
       </c>
       <c r="M56" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="N56" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O56" t="b">
         <v>0</v>
@@ -3146,31 +3149,31 @@
         <v>74</v>
       </c>
       <c r="D57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F57">
-        <v>539</v>
-      </c>
-      <c r="H57" t="s">
-        <v>120</v>
+        <v>175</v>
+      </c>
+      <c r="I57" t="s">
+        <v>122</v>
       </c>
       <c r="J57" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K57" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L57">
-        <v>539</v>
+        <v>0.26425</v>
       </c>
       <c r="M57" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="N57" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="O57" t="b">
         <v>0</v>
@@ -3187,31 +3190,31 @@
         <v>74</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F58">
-        <v>8.1</v>
-      </c>
-      <c r="H58" t="s">
-        <v>120</v>
+        <v>734.521</v>
+      </c>
+      <c r="I58" t="s">
+        <v>122</v>
       </c>
       <c r="J58" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K58" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L58">
-        <v>8.1</v>
+        <v>734.521</v>
       </c>
       <c r="M58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O58" t="b">
         <v>0</v>
@@ -3228,19 +3231,16 @@
         <v>74</v>
       </c>
       <c r="D59" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="E59" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F59">
-        <v>2599.5</v>
-      </c>
-      <c r="G59" t="s">
-        <v>110</v>
-      </c>
-      <c r="H59" t="s">
-        <v>121</v>
+        <v>5</v>
+      </c>
+      <c r="I59" t="s">
+        <v>122</v>
       </c>
       <c r="J59" t="s">
         <v>126</v>
@@ -3249,13 +3249,13 @@
         <v>132</v>
       </c>
       <c r="L59">
-        <v>2599.5</v>
+        <v>0.009200000000000002</v>
       </c>
       <c r="M59" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="N59" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="O59" t="b">
         <v>0</v>
@@ -3272,16 +3272,16 @@
         <v>74</v>
       </c>
       <c r="D60" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E60" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F60">
-        <v>1955.7</v>
-      </c>
-      <c r="H60" t="s">
-        <v>121</v>
+        <v>626.9835798</v>
+      </c>
+      <c r="I60" t="s">
+        <v>122</v>
       </c>
       <c r="J60" t="s">
         <v>126</v>
@@ -3290,13 +3290,13 @@
         <v>132</v>
       </c>
       <c r="L60">
-        <v>1955.7</v>
+        <v>626.9835798</v>
       </c>
       <c r="M60" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O60" t="b">
         <v>0</v>

--- a/data/MetalliCan/pre_cleaned_data/material_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/material_df.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_23F921ED36130D27D32D4C89E5B315F360A647D8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82394267-72C5-4958-BB4A-CFA3C906D1D7}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -454,8 +463,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,13 +527,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -562,7 +579,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -596,6 +613,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -630,9 +648,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -805,11 +824,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="66.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -856,7 +892,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -897,7 +933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -938,7 +974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -979,7 +1015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1020,7 +1056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1061,7 +1097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1102,7 +1138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1143,7 +1179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1184,7 +1220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1225,7 +1261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1254,7 +1290,7 @@
         <v>129</v>
       </c>
       <c r="L11">
-        <v>231.23982</v>
+        <v>231.23982000000001</v>
       </c>
       <c r="M11" t="s">
         <v>135</v>
@@ -1266,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1307,7 +1343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1324,7 +1360,7 @@
         <v>105</v>
       </c>
       <c r="F13">
-        <v>2269.57</v>
+        <v>2269.5700000000002</v>
       </c>
       <c r="H13" t="s">
         <v>112</v>
@@ -1336,7 +1372,7 @@
         <v>129</v>
       </c>
       <c r="L13">
-        <v>2269.57</v>
+        <v>2269.5700000000002</v>
       </c>
       <c r="M13" t="s">
         <v>105</v>
@@ -1348,7 +1384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1389,7 +1425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1430,7 +1466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1471,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1512,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1556,7 +1592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1597,7 +1633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1641,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1682,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -1699,7 +1735,7 @@
         <v>105</v>
       </c>
       <c r="F22">
-        <v>726.071</v>
+        <v>726.07100000000003</v>
       </c>
       <c r="G22" t="s">
         <v>110</v>
@@ -1714,7 +1750,7 @@
         <v>132</v>
       </c>
       <c r="L22">
-        <v>726.071</v>
+        <v>726.07100000000003</v>
       </c>
       <c r="M22" t="s">
         <v>105</v>
@@ -1726,7 +1762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1755,7 +1791,7 @@
         <v>132</v>
       </c>
       <c r="L23">
-        <v>68.068</v>
+        <v>68.067999999999998</v>
       </c>
       <c r="M23" t="s">
         <v>136</v>
@@ -1767,7 +1803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1784,7 +1820,7 @@
         <v>105</v>
       </c>
       <c r="F24">
-        <v>924.081</v>
+        <v>924.08100000000002</v>
       </c>
       <c r="H24" t="s">
         <v>116</v>
@@ -1796,7 +1832,7 @@
         <v>132</v>
       </c>
       <c r="L24">
-        <v>924.081</v>
+        <v>924.08100000000002</v>
       </c>
       <c r="M24" t="s">
         <v>105</v>
@@ -1808,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1825,7 +1861,7 @@
         <v>107</v>
       </c>
       <c r="F25">
-        <v>336.521</v>
+        <v>336.52100000000002</v>
       </c>
       <c r="H25" t="s">
         <v>116</v>
@@ -1837,7 +1873,7 @@
         <v>132</v>
       </c>
       <c r="L25">
-        <v>296.13848</v>
+        <v>296.13848000000002</v>
       </c>
       <c r="M25" t="s">
         <v>136</v>
@@ -1849,7 +1885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1866,7 +1902,7 @@
         <v>105</v>
       </c>
       <c r="F26">
-        <v>390.003</v>
+        <v>390.00299999999999</v>
       </c>
       <c r="H26" t="s">
         <v>116</v>
@@ -1878,7 +1914,7 @@
         <v>132</v>
       </c>
       <c r="L26">
-        <v>390.003</v>
+        <v>390.00299999999999</v>
       </c>
       <c r="M26" t="s">
         <v>105</v>
@@ -1890,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1931,7 +1967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -1972,7 +2008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -2013,7 +2049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -2030,7 +2066,7 @@
         <v>105</v>
       </c>
       <c r="F30">
-        <v>86.59999999999999</v>
+        <v>86.6</v>
       </c>
       <c r="H30" t="s">
         <v>117</v>
@@ -2042,7 +2078,7 @@
         <v>133</v>
       </c>
       <c r="L30">
-        <v>86.59999999999999</v>
+        <v>86.6</v>
       </c>
       <c r="M30" t="s">
         <v>105</v>
@@ -2054,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -2095,7 +2131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -2136,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -2180,7 +2216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -2221,7 +2257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -2262,7 +2298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -2303,7 +2339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2344,7 +2380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -2361,7 +2397,7 @@
         <v>105</v>
       </c>
       <c r="F38">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="H38" t="s">
         <v>117</v>
@@ -2373,7 +2409,7 @@
         <v>133</v>
       </c>
       <c r="L38">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="M38" t="s">
         <v>105</v>
@@ -2385,7 +2421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -2426,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -2467,7 +2503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -2508,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>55</v>
       </c>
@@ -2552,7 +2588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -2593,7 +2629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>57</v>
       </c>
@@ -2610,7 +2646,7 @@
         <v>107</v>
       </c>
       <c r="F44">
-        <v>380.687</v>
+        <v>380.68700000000001</v>
       </c>
       <c r="H44" t="s">
         <v>118</v>
@@ -2622,7 +2658,7 @@
         <v>132</v>
       </c>
       <c r="L44">
-        <v>335.00456</v>
+        <v>335.00456000000003</v>
       </c>
       <c r="M44" t="s">
         <v>136</v>
@@ -2634,7 +2670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>58</v>
       </c>
@@ -2663,7 +2699,7 @@
         <v>132</v>
       </c>
       <c r="L45">
-        <v>40.12825</v>
+        <v>40.128250000000001</v>
       </c>
       <c r="M45" t="s">
         <v>136</v>
@@ -2675,7 +2711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -2716,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -2733,7 +2769,7 @@
         <v>108</v>
       </c>
       <c r="F47">
-        <v>73.95999999999999</v>
+        <v>73.959999999999994</v>
       </c>
       <c r="H47" t="s">
         <v>118</v>
@@ -2757,7 +2793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -2774,7 +2810,7 @@
         <v>105</v>
       </c>
       <c r="F48">
-        <v>241.250567</v>
+        <v>241.25056699999999</v>
       </c>
       <c r="H48" t="s">
         <v>118</v>
@@ -2786,7 +2822,7 @@
         <v>132</v>
       </c>
       <c r="L48">
-        <v>241.250567</v>
+        <v>241.25056699999999</v>
       </c>
       <c r="M48" t="s">
         <v>105</v>
@@ -2798,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>62</v>
       </c>
@@ -2842,7 +2878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -2874,7 +2910,7 @@
         <v>134</v>
       </c>
       <c r="L50">
-        <v>2968.123704016</v>
+        <v>2968.1237040159999</v>
       </c>
       <c r="M50" t="s">
         <v>137</v>
@@ -2886,7 +2922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -2918,7 +2954,7 @@
         <v>134</v>
       </c>
       <c r="L51">
-        <v>231.88076632</v>
+        <v>231.88076631999999</v>
       </c>
       <c r="M51" t="s">
         <v>137</v>
@@ -2930,7 +2966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>65</v>
       </c>
@@ -2971,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -3015,7 +3051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>67</v>
       </c>
@@ -3032,7 +3068,7 @@
         <v>107</v>
       </c>
       <c r="F54">
-        <v>2.255</v>
+        <v>2.2549999999999999</v>
       </c>
       <c r="I54" t="s">
         <v>122</v>
@@ -3044,7 +3080,7 @@
         <v>132</v>
       </c>
       <c r="L54">
-        <v>2.68345</v>
+        <v>2.6834500000000001</v>
       </c>
       <c r="M54" t="s">
         <v>136</v>
@@ -3056,7 +3092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>68</v>
       </c>
@@ -3073,7 +3109,7 @@
         <v>105</v>
       </c>
       <c r="F55">
-        <v>4346.921</v>
+        <v>4346.9210000000003</v>
       </c>
       <c r="I55" t="s">
         <v>122</v>
@@ -3085,7 +3121,7 @@
         <v>132</v>
       </c>
       <c r="L55">
-        <v>4346.921</v>
+        <v>4346.9210000000003</v>
       </c>
       <c r="M55" t="s">
         <v>105</v>
@@ -3097,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -3114,7 +3150,7 @@
         <v>107</v>
       </c>
       <c r="F56">
-        <v>619.366</v>
+        <v>619.36599999999999</v>
       </c>
       <c r="I56" t="s">
         <v>122</v>
@@ -3126,7 +3162,7 @@
         <v>132</v>
       </c>
       <c r="L56">
-        <v>545.0420799999999</v>
+        <v>545.04207999999994</v>
       </c>
       <c r="M56" t="s">
         <v>136</v>
@@ -3138,7 +3174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>70</v>
       </c>
@@ -3167,7 +3203,7 @@
         <v>132</v>
       </c>
       <c r="L57">
-        <v>0.26425</v>
+        <v>0.26424999999999998</v>
       </c>
       <c r="M57" t="s">
         <v>136</v>
@@ -3179,7 +3215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>71</v>
       </c>
@@ -3196,7 +3232,7 @@
         <v>105</v>
       </c>
       <c r="F58">
-        <v>734.521</v>
+        <v>734.52099999999996</v>
       </c>
       <c r="I58" t="s">
         <v>122</v>
@@ -3208,7 +3244,7 @@
         <v>132</v>
       </c>
       <c r="L58">
-        <v>734.521</v>
+        <v>734.52099999999996</v>
       </c>
       <c r="M58" t="s">
         <v>105</v>
@@ -3220,7 +3256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -3249,7 +3285,7 @@
         <v>132</v>
       </c>
       <c r="L59">
-        <v>0.009200000000000002</v>
+        <v>9.2000000000000016E-3</v>
       </c>
       <c r="M59" t="s">
         <v>136</v>
@@ -3261,7 +3297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>73</v>
       </c>
@@ -3278,7 +3314,7 @@
         <v>105</v>
       </c>
       <c r="F60">
-        <v>626.9835798</v>
+        <v>626.98357980000003</v>
       </c>
       <c r="I60" t="s">
         <v>122</v>
@@ -3290,7 +3326,7 @@
         <v>132</v>
       </c>
       <c r="L60">
-        <v>626.9835798</v>
+        <v>626.98357980000003</v>
       </c>
       <c r="M60" t="s">
         <v>105</v>
@@ -3303,6 +3339,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/material_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/material_df.xlsx
@@ -1,24 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_23F921ED36130D27D32D4C89E5B315F360A647D8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82394267-72C5-4958-BB4A-CFA3C906D1D7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$1</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -70,6 +61,69 @@
     <t>needs_density</t>
   </si>
   <si>
+    <t>TECH-b86f7d07-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-cb85213a-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-12.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-13.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-44857446-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-9de9bb0d-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-11.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-13.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-15.0</t>
+  </si>
+  <si>
     <t>TECH-aa76f6f2-2023.0-1.0</t>
   </si>
   <si>
@@ -91,6 +145,33 @@
     <t>TECH-aa76f6f2-2023.0-14.0</t>
   </si>
   <si>
+    <t>TECH-GRP-0d911886-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-12.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-15.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0d911886-2023.0-16.0</t>
+  </si>
+  <si>
     <t>TECH-0aadf28f-2023.0-1.0</t>
   </si>
   <si>
@@ -112,10 +193,43 @@
     <t>TECH-0aadf28f-2023.0-11.0</t>
   </si>
   <si>
-    <t>TECH-687b8c8d-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-687b8c8d-2023.0-7.0</t>
+    <t>TECH-02884fb5-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-11.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-13.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-15.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-16.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-19.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-20.0</t>
   </si>
   <si>
     <t>TECH-7607a50e-2023.0-7.0</t>
@@ -124,132 +238,48 @@
     <t>TECH-7607a50e-2023.0-8.0</t>
   </si>
   <si>
-    <t>TECH-cb85213a-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-8.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-9.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-10.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-11.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-13.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-15.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-10.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-11.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-13.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-14.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-15.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-16.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-19.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-20.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-7.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-8.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-9.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-10.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-12.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-13.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-14.0</t>
-  </si>
-  <si>
-    <t>TECH-9de9bb0d-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-b86f7d07-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-44857446-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023.0-7.0</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023.0-8.0</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023.0-9.0</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023.0-10.0</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023.0-12.0</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023.0-14.0</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023.0-15.0</t>
-  </si>
-  <si>
-    <t>TECH-GRP-0d911886-2023.0-16.0</t>
-  </si>
-  <si>
     <t>Material use</t>
   </si>
   <si>
+    <t>Surface/underground emulsion &amp; ANFO</t>
+  </si>
+  <si>
+    <t>Explosives</t>
+  </si>
+  <si>
+    <t>Cement</t>
+  </si>
+  <si>
+    <t>Grinding media</t>
+  </si>
+  <si>
+    <t>Lime</t>
+  </si>
+  <si>
+    <t>Lubricants</t>
+  </si>
+  <si>
+    <t>Nitric acid (HNO3)</t>
+  </si>
+  <si>
+    <t>Sodium cyanide (NaCN)</t>
+  </si>
+  <si>
+    <t>Sulfuric acid (H2SO4)</t>
+  </si>
+  <si>
+    <t>Tires</t>
+  </si>
+  <si>
+    <t>Total blasting agents used e.g. ANFO</t>
+  </si>
+  <si>
+    <t>Total sodium cyanide used</t>
+  </si>
+  <si>
+    <t>Hydrochloric acid (HCL)</t>
+  </si>
+  <si>
     <t>2'' balls</t>
   </si>
   <si>
@@ -262,9 +292,6 @@
     <t>Flocculant</t>
   </si>
   <si>
-    <t>Lime</t>
-  </si>
-  <si>
     <t>Polyfroth h57</t>
   </si>
   <si>
@@ -283,33 +310,6 @@
     <t>Cyanide</t>
   </si>
   <si>
-    <t>Total blasting agents used e.g. ANFO</t>
-  </si>
-  <si>
-    <t>Total sodium cyanide used</t>
-  </si>
-  <si>
-    <t>Explosives</t>
-  </si>
-  <si>
-    <t>Cement</t>
-  </si>
-  <si>
-    <t>Grinding media</t>
-  </si>
-  <si>
-    <t>Hydrochloric acid (HCL)</t>
-  </si>
-  <si>
-    <t>Lubricants</t>
-  </si>
-  <si>
-    <t>Sodium cyanide (NaCN)</t>
-  </si>
-  <si>
-    <t>Tires</t>
-  </si>
-  <si>
     <t>Carbon</t>
   </si>
   <si>
@@ -331,140 +331,131 @@
     <t>Transmission oil</t>
   </si>
   <si>
-    <t>Nitric acid (HNO3)</t>
-  </si>
-  <si>
-    <t>Sulfuric acid (H2SO4)</t>
-  </si>
-  <si>
-    <t>Surface/underground emulsion &amp; ANFO</t>
+    <t>pounds</t>
   </si>
   <si>
     <t>t</t>
   </si>
   <si>
+    <t>kl</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
     <t>kg</t>
   </si>
   <si>
-    <t>kl</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>Explosives, treated as material input because in t</t>
   </si>
   <si>
+    <t>QC-MAIN-b86f7d07</t>
+  </si>
+  <si>
+    <t>ON-MAIN-cb85213a</t>
+  </si>
+  <si>
+    <t>QC-MAIN-6dc537e6</t>
+  </si>
+  <si>
+    <t>ON-MAIN-687b8c8d</t>
+  </si>
+  <si>
+    <t>YT-MAIN-44857446</t>
+  </si>
+  <si>
+    <t>QC-MAIN-9de9bb0d</t>
+  </si>
+  <si>
+    <t>ON-MAIN-fefeaee4</t>
+  </si>
+  <si>
     <t>BC-MAIN-aa76f6f2</t>
   </si>
   <si>
     <t>ON-MAIN-0aadf28f</t>
   </si>
   <si>
-    <t>ON-MAIN-687b8c8d</t>
+    <t>QC-MAIN-02884fb5</t>
   </si>
   <si>
     <t>ON-MAIN-7607a50e</t>
   </si>
   <si>
-    <t>ON-MAIN-cb85213a</t>
-  </si>
-  <si>
-    <t>ON-MAIN-fefeaee4</t>
-  </si>
-  <si>
-    <t>QC-MAIN-02884fb5</t>
-  </si>
-  <si>
-    <t>QC-MAIN-6dc537e6</t>
-  </si>
-  <si>
-    <t>QC-MAIN-9de9bb0d</t>
-  </si>
-  <si>
-    <t>QC-MAIN-b86f7d07</t>
-  </si>
-  <si>
-    <t>YT-MAIN-44857446</t>
-  </si>
-  <si>
     <t>GRP-0d911886</t>
   </si>
   <si>
+    <t>CMP-7e360a1f</t>
+  </si>
+  <si>
+    <t>CMP-3d2c4955</t>
+  </si>
+  <si>
+    <t>CMP-4a434d72</t>
+  </si>
+  <si>
+    <t>CMP-3a4ccc7f</t>
+  </si>
+  <si>
     <t>CMP-d94be190</t>
   </si>
   <si>
-    <t>CMP-3a4ccc7f</t>
-  </si>
-  <si>
-    <t>CMP-3d2c4955</t>
-  </si>
-  <si>
-    <t>CMP-4a434d72</t>
-  </si>
-  <si>
     <t>CMP-3d0a95b7</t>
   </si>
   <si>
-    <t>CMP-7e360a1f</t>
+    <t>HeclaMiningCompany_SR_2023</t>
+  </si>
+  <si>
+    <t>WesdomeGoldMinesLtd._ESG_data_2023</t>
+  </si>
+  <si>
+    <t>NewmontCorporation_Newmont-2023-Performance-Data-Tables-V4-locked</t>
+  </si>
+  <si>
+    <t>AlamosGoldInc_Data_2023</t>
   </si>
   <si>
     <t>NewGoldInc_2023-New-Gold-ESG-Data-Factbook</t>
   </si>
   <si>
-    <t>AlamosGoldInc_Data_2023</t>
-  </si>
-  <si>
-    <t>WesdomeGoldMinesLtd._ESG_data_2023</t>
-  </si>
-  <si>
-    <t>NewmontCorporation_Newmont-2023-Performance-Data-Tables-V4-locked</t>
-  </si>
-  <si>
     <t>IAMGOLDCorporation_2023_iamgold-esg-performance-data-final_protected</t>
   </si>
   <si>
-    <t>HeclaMiningCompany_SR_2023</t>
+    <t>lbs→t</t>
+  </si>
+  <si>
+    <t>L×density→t</t>
   </si>
   <si>
     <t>kg→t</t>
   </si>
   <si>
-    <t>L×density→t</t>
-  </si>
-  <si>
-    <t>lbs→t</t>
+    <t>lbs×0.453592/1000</t>
   </si>
   <si>
     <t>reported in tonnes</t>
   </si>
   <si>
+    <t>kl×density=0.88 kg/L</t>
+  </si>
+  <si>
+    <t>l×density=1.51 kg/L</t>
+  </si>
+  <si>
+    <t>l×density=1.84 kg/L</t>
+  </si>
+  <si>
+    <t>kl×density=1.19 kg/L</t>
+  </si>
+  <si>
     <t>kg/1000</t>
-  </si>
-  <si>
-    <t>kl×density=1.19 kg/L</t>
-  </si>
-  <si>
-    <t>kl×density=0.88 kg/L</t>
-  </si>
-  <si>
-    <t>l×density=1.51 kg/L</t>
-  </si>
-  <si>
-    <t>l×density=1.84 kg/L</t>
-  </si>
-  <si>
-    <t>lbs×0.453592/1000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,21 +518,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -579,7 +562,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -613,7 +596,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -648,10 +630,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -824,28 +805,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="28.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="66.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.36328125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -892,7 +856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -909,7 +873,10 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>980</v>
+        <v>6543598</v>
+      </c>
+      <c r="G2" t="s">
+        <v>110</v>
       </c>
       <c r="H2" t="s">
         <v>111</v>
@@ -921,10 +888,10 @@
         <v>129</v>
       </c>
       <c r="L2">
-        <v>980</v>
+        <v>2968.123704016</v>
       </c>
       <c r="M2" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="N2" t="s">
         <v>138</v>
@@ -933,7 +900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -947,34 +914,37 @@
         <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F3">
-        <v>179</v>
+        <v>1211</v>
+      </c>
+      <c r="G3" t="s">
+        <v>110</v>
       </c>
       <c r="H3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L3">
-        <v>179</v>
+        <v>1211</v>
       </c>
       <c r="M3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -991,22 +961,22 @@
         <v>106</v>
       </c>
       <c r="F4">
-        <v>38000</v>
+        <v>27374</v>
       </c>
       <c r="H4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L4">
-        <v>38</v>
+        <v>27374</v>
       </c>
       <c r="M4" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="N4" t="s">
         <v>139</v>
@@ -1015,7 +985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1029,34 +999,37 @@
         <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F5">
-        <v>192</v>
+        <v>3039.9</v>
+      </c>
+      <c r="G5" t="s">
+        <v>110</v>
       </c>
       <c r="H5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L5">
-        <v>192</v>
+        <v>3039.9</v>
       </c>
       <c r="M5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1070,34 +1043,34 @@
         <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F6">
-        <v>2724</v>
+        <v>2229</v>
       </c>
       <c r="H6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L6">
-        <v>2724</v>
+        <v>2229</v>
       </c>
       <c r="M6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1111,34 +1084,34 @@
         <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>55</v>
+        <v>380.687</v>
       </c>
       <c r="H7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L7">
-        <v>55</v>
+        <v>335.00456</v>
       </c>
       <c r="M7" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1152,34 +1125,34 @@
         <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F8">
-        <v>583</v>
+        <v>26575</v>
       </c>
       <c r="H8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L8">
-        <v>583</v>
+        <v>40.12825</v>
       </c>
       <c r="M8" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1193,34 +1166,34 @@
         <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F9">
-        <v>5977.02</v>
+        <v>838.8</v>
       </c>
       <c r="H9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L9">
-        <v>5977.02</v>
+        <v>838.8</v>
       </c>
       <c r="M9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1234,34 +1207,34 @@
         <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F10">
-        <v>2819.39</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L10">
-        <v>2819.39</v>
+        <v>0.1360864</v>
       </c>
       <c r="M10" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1272,28 +1245,28 @@
         <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>106</v>
       </c>
       <c r="F11">
-        <v>231239.82</v>
+        <v>241.250566996281</v>
       </c>
       <c r="H11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L11">
-        <v>231.23982000000001</v>
+        <v>241.250566996281</v>
       </c>
       <c r="M11" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="N11" t="s">
         <v>139</v>
@@ -1302,7 +1275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1313,37 +1286,37 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F12">
-        <v>526.21</v>
+        <v>486.3</v>
       </c>
       <c r="H12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L12">
-        <v>526.21</v>
+        <v>486.3</v>
       </c>
       <c r="M12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1354,37 +1327,37 @@
         <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F13">
-        <v>2269.5700000000002</v>
+        <v>245</v>
       </c>
       <c r="H13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L13">
-        <v>2269.5700000000002</v>
+        <v>245</v>
       </c>
       <c r="M13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1395,16 +1368,19 @@
         <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>105</v>
       </c>
       <c r="F14">
-        <v>149.1</v>
+        <v>511210</v>
+      </c>
+      <c r="G14" t="s">
+        <v>110</v>
       </c>
       <c r="H14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J14" t="s">
         <v>123</v>
@@ -1413,10 +1389,10 @@
         <v>129</v>
       </c>
       <c r="L14">
-        <v>149.1</v>
+        <v>231.88076632</v>
       </c>
       <c r="M14" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="N14" t="s">
         <v>138</v>
@@ -1425,7 +1401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1436,37 +1412,40 @@
         <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F15">
-        <v>6390.4</v>
+        <v>506</v>
+      </c>
+      <c r="G15" t="s">
+        <v>110</v>
       </c>
       <c r="H15" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L15">
-        <v>6390.4</v>
+        <v>506</v>
       </c>
       <c r="M15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1477,37 +1456,37 @@
         <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F16">
-        <v>486.3</v>
+        <v>9417.6</v>
       </c>
       <c r="H16" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L16">
-        <v>486.3</v>
+        <v>9417.6</v>
       </c>
       <c r="M16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1518,37 +1497,40 @@
         <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F17">
-        <v>245</v>
+        <v>726.071</v>
+      </c>
+      <c r="G17" t="s">
+        <v>110</v>
       </c>
       <c r="H17" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L17">
-        <v>245</v>
+        <v>726.071</v>
       </c>
       <c r="M17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1559,40 +1541,37 @@
         <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F18">
-        <v>2599.5</v>
-      </c>
-      <c r="G18" t="s">
-        <v>110</v>
+        <v>57.2</v>
       </c>
       <c r="H18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L18">
-        <v>2599.5</v>
+        <v>68.068</v>
       </c>
       <c r="M18" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N18" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1603,37 +1582,37 @@
         <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F19">
-        <v>1955.7</v>
+        <v>924.081</v>
       </c>
       <c r="H19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L19">
-        <v>1955.7</v>
+        <v>924.081</v>
       </c>
       <c r="M19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1644,19 +1623,16 @@
         <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F20">
-        <v>1211</v>
-      </c>
-      <c r="G20" t="s">
-        <v>110</v>
+        <v>336.521</v>
       </c>
       <c r="H20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J20" t="s">
         <v>125</v>
@@ -1665,19 +1641,19 @@
         <v>131</v>
       </c>
       <c r="L20">
-        <v>1211</v>
+        <v>296.13848</v>
       </c>
       <c r="M20" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1688,37 +1664,37 @@
         <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F21">
-        <v>9417.6</v>
+        <v>390.003</v>
       </c>
       <c r="H21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L21">
-        <v>9417.6</v>
+        <v>390.003</v>
       </c>
       <c r="M21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -1729,40 +1705,37 @@
         <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F22">
-        <v>726.07100000000003</v>
-      </c>
-      <c r="G22" t="s">
-        <v>110</v>
+        <v>100.705343372947</v>
       </c>
       <c r="H22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L22">
-        <v>726.07100000000003</v>
+        <v>100.705343372947</v>
       </c>
       <c r="M22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1773,37 +1746,37 @@
         <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F23">
-        <v>57.2</v>
+        <v>980</v>
       </c>
       <c r="H23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L23">
-        <v>68.067999999999998</v>
+        <v>980</v>
       </c>
       <c r="M23" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1814,37 +1787,37 @@
         <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F24">
-        <v>924.08100000000002</v>
+        <v>179</v>
       </c>
       <c r="H24" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L24">
-        <v>924.08100000000002</v>
+        <v>179</v>
       </c>
       <c r="M24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1855,37 +1828,37 @@
         <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F25">
-        <v>336.52100000000002</v>
+        <v>38000</v>
       </c>
       <c r="H25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L25">
-        <v>296.13848000000002</v>
+        <v>38</v>
       </c>
       <c r="M25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N25" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1896,37 +1869,37 @@
         <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26">
-        <v>390.00299999999999</v>
+        <v>192</v>
       </c>
       <c r="H26" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L26">
-        <v>390.00299999999999</v>
+        <v>192</v>
       </c>
       <c r="M26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1937,37 +1910,37 @@
         <v>74</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F27">
-        <v>100.7053434</v>
+        <v>2724</v>
       </c>
       <c r="H27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L27">
-        <v>100.7053434</v>
+        <v>2724</v>
       </c>
       <c r="M27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -1978,16 +1951,16 @@
         <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F28">
-        <v>35.4</v>
+        <v>55</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J28" t="s">
         <v>127</v>
@@ -1996,19 +1969,19 @@
         <v>133</v>
       </c>
       <c r="L28">
-        <v>35.4</v>
+        <v>55</v>
       </c>
       <c r="M28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -2019,16 +1992,16 @@
         <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F29">
-        <v>60.4</v>
+        <v>583</v>
       </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J29" t="s">
         <v>127</v>
@@ -2037,19 +2010,19 @@
         <v>133</v>
       </c>
       <c r="L29">
-        <v>60.4</v>
+        <v>583</v>
       </c>
       <c r="M29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O29" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -2060,37 +2033,37 @@
         <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F30">
-        <v>86.6</v>
-      </c>
-      <c r="H30" t="s">
-        <v>117</v>
+        <v>12578</v>
+      </c>
+      <c r="I30" t="s">
+        <v>122</v>
       </c>
       <c r="J30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K30" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L30">
-        <v>86.6</v>
+        <v>12578</v>
       </c>
       <c r="M30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O30" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -2101,37 +2074,40 @@
         <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F31">
-        <v>1.5</v>
-      </c>
-      <c r="H31" t="s">
-        <v>117</v>
+        <v>1932.222</v>
+      </c>
+      <c r="G31" t="s">
+        <v>110</v>
+      </c>
+      <c r="I31" t="s">
+        <v>122</v>
       </c>
       <c r="J31" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K31" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L31">
-        <v>1.5</v>
+        <v>1932.222</v>
       </c>
       <c r="M31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -2142,37 +2118,37 @@
         <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F32">
-        <v>399.3</v>
-      </c>
-      <c r="H32" t="s">
-        <v>117</v>
+        <v>2.255</v>
+      </c>
+      <c r="I32" t="s">
+        <v>122</v>
       </c>
       <c r="J32" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K32" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L32">
-        <v>399.3</v>
+        <v>2.68345</v>
       </c>
       <c r="M32" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N32" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -2183,40 +2159,37 @@
         <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F33">
-        <v>1483.4</v>
-      </c>
-      <c r="G33" t="s">
-        <v>110</v>
-      </c>
-      <c r="H33" t="s">
-        <v>117</v>
+        <v>4346.921</v>
+      </c>
+      <c r="I33" t="s">
+        <v>122</v>
       </c>
       <c r="J33" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L33">
-        <v>1483.4</v>
+        <v>4346.921</v>
       </c>
       <c r="M33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -2227,37 +2200,37 @@
         <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F34">
-        <v>46.2</v>
-      </c>
-      <c r="H34" t="s">
-        <v>117</v>
+        <v>619.366</v>
+      </c>
+      <c r="I34" t="s">
+        <v>122</v>
       </c>
       <c r="J34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L34">
-        <v>46.2</v>
+        <v>545.0420799999999</v>
       </c>
       <c r="M34" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N34" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -2268,37 +2241,37 @@
         <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F35">
-        <v>4.5</v>
-      </c>
-      <c r="H35" t="s">
-        <v>117</v>
+        <v>175</v>
+      </c>
+      <c r="I35" t="s">
+        <v>122</v>
       </c>
       <c r="J35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L35">
-        <v>4.5</v>
+        <v>0.26425</v>
       </c>
       <c r="M35" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N35" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -2309,37 +2282,37 @@
         <v>74</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F36">
-        <v>200.2</v>
-      </c>
-      <c r="H36" t="s">
-        <v>117</v>
+        <v>734.521</v>
+      </c>
+      <c r="I36" t="s">
+        <v>122</v>
       </c>
       <c r="J36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L36">
-        <v>200.2</v>
+        <v>734.521</v>
       </c>
       <c r="M36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2350,37 +2323,37 @@
         <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E37" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F37">
-        <v>5069.3</v>
-      </c>
-      <c r="H37" t="s">
-        <v>117</v>
+        <v>5</v>
+      </c>
+      <c r="I37" t="s">
+        <v>122</v>
       </c>
       <c r="J37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L37">
-        <v>5069.3</v>
+        <v>0.009200000000000002</v>
       </c>
       <c r="M37" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="N37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -2391,37 +2364,37 @@
         <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F38">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="H38" t="s">
-        <v>117</v>
+        <v>626.983579787717</v>
+      </c>
+      <c r="I38" t="s">
+        <v>122</v>
       </c>
       <c r="J38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L38">
-        <v>18.899999999999999</v>
+        <v>626.983579787717</v>
       </c>
       <c r="M38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -2432,16 +2405,16 @@
         <v>74</v>
       </c>
       <c r="D39" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F39">
-        <v>539</v>
+        <v>5977.02</v>
       </c>
       <c r="H39" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J39" t="s">
         <v>127</v>
@@ -2450,19 +2423,19 @@
         <v>133</v>
       </c>
       <c r="L39">
-        <v>539</v>
+        <v>5977.02</v>
       </c>
       <c r="M39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O39" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -2473,16 +2446,16 @@
         <v>74</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F40">
-        <v>8.1</v>
+        <v>2819.39</v>
       </c>
       <c r="H40" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J40" t="s">
         <v>127</v>
@@ -2491,19 +2464,19 @@
         <v>133</v>
       </c>
       <c r="L40">
-        <v>8.1</v>
+        <v>2819.39</v>
       </c>
       <c r="M40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -2514,37 +2487,37 @@
         <v>74</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F41">
-        <v>27374</v>
+        <v>231239.82</v>
       </c>
       <c r="H41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K41" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L41">
-        <v>27374</v>
+        <v>231.23982</v>
       </c>
       <c r="M41" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="N41" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
         <v>55</v>
       </c>
@@ -2555,40 +2528,37 @@
         <v>74</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F42">
-        <v>3039.9</v>
-      </c>
-      <c r="G42" t="s">
-        <v>110</v>
+        <v>526.21</v>
       </c>
       <c r="H42" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J42" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K42" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L42">
-        <v>3039.9</v>
+        <v>526.21</v>
       </c>
       <c r="M42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -2599,37 +2569,37 @@
         <v>74</v>
       </c>
       <c r="D43" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F43">
-        <v>2229</v>
+        <v>2269.57</v>
       </c>
       <c r="H43" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J43" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K43" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L43">
-        <v>2229</v>
+        <v>2269.57</v>
       </c>
       <c r="M43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N43" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O43" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
         <v>57</v>
       </c>
@@ -2640,37 +2610,37 @@
         <v>74</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F44">
-        <v>380.68700000000001</v>
+        <v>149.1</v>
       </c>
       <c r="H44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K44" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L44">
-        <v>335.00456000000003</v>
+        <v>149.1</v>
       </c>
       <c r="M44" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
         <v>58</v>
       </c>
@@ -2681,37 +2651,37 @@
         <v>74</v>
       </c>
       <c r="D45" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E45" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F45">
-        <v>26575</v>
+        <v>6390.4</v>
       </c>
       <c r="H45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K45" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L45">
-        <v>40.128250000000001</v>
+        <v>6390.4</v>
       </c>
       <c r="M45" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N45" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O45" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -2722,37 +2692,37 @@
         <v>74</v>
       </c>
       <c r="D46" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F46">
-        <v>838.8</v>
+        <v>35.4</v>
       </c>
       <c r="H46" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J46" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K46" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L46">
-        <v>838.8</v>
+        <v>35.4</v>
       </c>
       <c r="M46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N46" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O46" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -2763,37 +2733,37 @@
         <v>74</v>
       </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E47" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F47">
-        <v>73.959999999999994</v>
+        <v>60.4</v>
       </c>
       <c r="H47" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K47" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L47">
-        <v>0.1360864</v>
+        <v>60.4</v>
       </c>
       <c r="M47" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N47" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O47" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -2804,37 +2774,37 @@
         <v>74</v>
       </c>
       <c r="D48" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F48">
-        <v>241.25056699999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H48" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K48" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L48">
-        <v>241.25056699999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="M48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O48" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
         <v>62</v>
       </c>
@@ -2845,40 +2815,37 @@
         <v>74</v>
       </c>
       <c r="D49" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E49" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F49">
-        <v>506</v>
-      </c>
-      <c r="G49" t="s">
-        <v>110</v>
+        <v>1.5</v>
       </c>
       <c r="H49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J49" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K49" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L49">
-        <v>506</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N49" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O49" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -2889,16 +2856,13 @@
         <v>74</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E50" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F50">
-        <v>6543598</v>
-      </c>
-      <c r="G50" t="s">
-        <v>110</v>
+        <v>399.3</v>
       </c>
       <c r="H50" t="s">
         <v>120</v>
@@ -2910,19 +2874,19 @@
         <v>134</v>
       </c>
       <c r="L50">
-        <v>2968.1237040159999</v>
+        <v>399.3</v>
       </c>
       <c r="M50" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="N50" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="O50" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -2933,19 +2897,19 @@
         <v>74</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="E51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F51">
-        <v>511210</v>
+        <v>1483.4</v>
       </c>
       <c r="G51" t="s">
         <v>110</v>
       </c>
       <c r="H51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J51" t="s">
         <v>128</v>
@@ -2954,19 +2918,19 @@
         <v>134</v>
       </c>
       <c r="L51">
-        <v>231.88076631999999</v>
+        <v>1483.4</v>
       </c>
       <c r="M51" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="N51" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="O51" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
         <v>65</v>
       </c>
@@ -2977,37 +2941,37 @@
         <v>74</v>
       </c>
       <c r="D52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F52">
-        <v>12578</v>
-      </c>
-      <c r="I52" t="s">
-        <v>122</v>
+        <v>46.2</v>
+      </c>
+      <c r="H52" t="s">
+        <v>120</v>
       </c>
       <c r="J52" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K52" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L52">
-        <v>12578</v>
+        <v>46.2</v>
       </c>
       <c r="M52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N52" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O52" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -3018,40 +2982,37 @@
         <v>74</v>
       </c>
       <c r="D53" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F53">
-        <v>1932.222</v>
-      </c>
-      <c r="G53" t="s">
-        <v>110</v>
-      </c>
-      <c r="I53" t="s">
-        <v>122</v>
+        <v>4.5</v>
+      </c>
+      <c r="H53" t="s">
+        <v>120</v>
       </c>
       <c r="J53" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K53" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L53">
-        <v>1932.222</v>
+        <v>4.5</v>
       </c>
       <c r="M53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N53" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O53" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15">
       <c r="A54" t="s">
         <v>67</v>
       </c>
@@ -3062,37 +3023,37 @@
         <v>74</v>
       </c>
       <c r="D54" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E54" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F54">
-        <v>2.2549999999999999</v>
-      </c>
-      <c r="I54" t="s">
-        <v>122</v>
+        <v>200.2</v>
+      </c>
+      <c r="H54" t="s">
+        <v>120</v>
       </c>
       <c r="J54" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L54">
-        <v>2.6834500000000001</v>
+        <v>200.2</v>
       </c>
       <c r="M54" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O54" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15">
       <c r="A55" t="s">
         <v>68</v>
       </c>
@@ -3106,34 +3067,34 @@
         <v>79</v>
       </c>
       <c r="E55" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F55">
-        <v>4346.9210000000003</v>
-      </c>
-      <c r="I55" t="s">
-        <v>122</v>
+        <v>5069.3</v>
+      </c>
+      <c r="H55" t="s">
+        <v>120</v>
       </c>
       <c r="J55" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K55" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L55">
-        <v>4346.9210000000003</v>
+        <v>5069.3</v>
       </c>
       <c r="M55" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O55" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -3144,37 +3105,37 @@
         <v>74</v>
       </c>
       <c r="D56" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F56">
-        <v>619.36599999999999</v>
-      </c>
-      <c r="I56" t="s">
-        <v>122</v>
+        <v>18.9</v>
+      </c>
+      <c r="H56" t="s">
+        <v>120</v>
       </c>
       <c r="J56" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K56" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L56">
-        <v>545.04207999999994</v>
+        <v>18.9</v>
       </c>
       <c r="M56" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N56" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O56" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15">
       <c r="A57" t="s">
         <v>70</v>
       </c>
@@ -3185,37 +3146,37 @@
         <v>74</v>
       </c>
       <c r="D57" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E57" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F57">
-        <v>175</v>
-      </c>
-      <c r="I57" t="s">
-        <v>122</v>
+        <v>539</v>
+      </c>
+      <c r="H57" t="s">
+        <v>120</v>
       </c>
       <c r="J57" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K57" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L57">
-        <v>0.26424999999999998</v>
+        <v>539</v>
       </c>
       <c r="M57" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N57" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15">
       <c r="A58" t="s">
         <v>71</v>
       </c>
@@ -3226,37 +3187,37 @@
         <v>74</v>
       </c>
       <c r="D58" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E58" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F58">
-        <v>734.52099999999996</v>
-      </c>
-      <c r="I58" t="s">
-        <v>122</v>
+        <v>8.1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>120</v>
       </c>
       <c r="J58" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K58" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L58">
-        <v>734.52099999999996</v>
+        <v>8.1</v>
       </c>
       <c r="M58" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N58" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O58" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -3267,16 +3228,19 @@
         <v>74</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E59" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F59">
-        <v>5</v>
-      </c>
-      <c r="I59" t="s">
-        <v>122</v>
+        <v>2599.5</v>
+      </c>
+      <c r="G59" t="s">
+        <v>110</v>
+      </c>
+      <c r="H59" t="s">
+        <v>121</v>
       </c>
       <c r="J59" t="s">
         <v>126</v>
@@ -3285,19 +3249,19 @@
         <v>132</v>
       </c>
       <c r="L59">
-        <v>9.2000000000000016E-3</v>
+        <v>2599.5</v>
       </c>
       <c r="M59" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N59" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O59" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15">
       <c r="A60" t="s">
         <v>73</v>
       </c>
@@ -3308,16 +3272,16 @@
         <v>74</v>
       </c>
       <c r="D60" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F60">
-        <v>626.98357980000003</v>
-      </c>
-      <c r="I60" t="s">
-        <v>122</v>
+        <v>1955.7</v>
+      </c>
+      <c r="H60" t="s">
+        <v>121</v>
       </c>
       <c r="J60" t="s">
         <v>126</v>
@@ -3326,20 +3290,19 @@
         <v>132</v>
       </c>
       <c r="L60">
-        <v>626.98357980000003</v>
+        <v>1955.7</v>
       </c>
       <c r="M60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N60" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O60" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/material_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/material_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="184">
   <si>
     <t>technosphere_id</t>
   </si>
@@ -64,6 +64,9 @@
     <t>TECH-b86f7d07-2023.0-5.0</t>
   </si>
   <si>
+    <t>TECH-aeafbb59-2023.0-3.0</t>
+  </si>
+  <si>
     <t>TECH-cb85213a-2023.0-4.0</t>
   </si>
   <si>
@@ -91,6 +94,9 @@
     <t>TECH-6dc537e6-2023.0-14.0</t>
   </si>
   <si>
+    <t>TECH-c0660aec-2023.0-3.0</t>
+  </si>
+  <si>
     <t>TECH-687b8c8d-2023.0-6.0</t>
   </si>
   <si>
@@ -103,6 +109,21 @@
     <t>TECH-9de9bb0d-2023.0-4.0</t>
   </si>
   <si>
+    <t>TECH-e51eda66-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-1f126a43-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-0a2c0d69-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-8b0264c9-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-ed23117f-2023.0-3.0</t>
+  </si>
+  <si>
     <t>TECH-fefeaee4-2023.0-3.0</t>
   </si>
   <si>
@@ -133,6 +154,9 @@
     <t>TECH-aa76f6f2-2023.0-3.0</t>
   </si>
   <si>
+    <t>TECH-aa76f6f2-2023.0-7.0</t>
+  </si>
+  <si>
     <t>TECH-aa76f6f2-2023.0-8.0</t>
   </si>
   <si>
@@ -187,12 +211,27 @@
     <t>TECH-0aadf28f-2023.0-5.0</t>
   </si>
   <si>
+    <t>TECH-0aadf28f-2023.0-8.0</t>
+  </si>
+  <si>
     <t>TECH-0aadf28f-2023.0-9.0</t>
   </si>
   <si>
     <t>TECH-0aadf28f-2023.0-11.0</t>
   </si>
   <si>
+    <t>TECH-GRP-147b3123-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-147b3123-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-GRP-147b3123-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-1.0</t>
+  </si>
+  <si>
     <t>TECH-02884fb5-2023.0-2.0</t>
   </si>
   <si>
@@ -208,6 +247,9 @@
     <t>TECH-02884fb5-2023.0-6.0</t>
   </si>
   <si>
+    <t>TECH-02884fb5-2023.0-9.0</t>
+  </si>
+  <si>
     <t>TECH-02884fb5-2023.0-10.0</t>
   </si>
   <si>
@@ -310,12 +352,27 @@
     <t>Cyanide</t>
   </si>
   <si>
+    <t>Ammonium nitrate</t>
+  </si>
+  <si>
+    <t>Dynamite</t>
+  </si>
+  <si>
+    <t>Emulsions</t>
+  </si>
+  <si>
+    <t>ANFO</t>
+  </si>
+  <si>
     <t>Carbon</t>
   </si>
   <si>
     <t>Compressor oil</t>
   </si>
   <si>
+    <t>Emulsion ANFO</t>
+  </si>
+  <si>
     <t>Grease</t>
   </si>
   <si>
@@ -334,6 +391,9 @@
     <t>pounds</t>
   </si>
   <si>
+    <t>GJ</t>
+  </si>
+  <si>
     <t>t</t>
   </si>
   <si>
@@ -349,15 +409,27 @@
     <t>Explosives, treated as material input because in t</t>
   </si>
   <si>
+    <t>Data initially in tCO2eq; back calculated with emission factors: 74.1kgCO2eq/GJ for diesel, 69.9kgCO2eq/GJ for gasoline, 59.9kgCO2eq/GJ for propane, BC mix 12kgCO2eq/MWh, explosives 3.75GJ/tCO2</t>
+  </si>
+  <si>
+    <t>Explosives, treated as material usage</t>
+  </si>
+  <si>
     <t>QC-MAIN-b86f7d07</t>
   </si>
   <si>
+    <t>ON-MAIN-aeafbb59</t>
+  </si>
+  <si>
     <t>ON-MAIN-cb85213a</t>
   </si>
   <si>
     <t>QC-MAIN-6dc537e6</t>
   </si>
   <si>
+    <t>QC-MAIN-c0660aec</t>
+  </si>
+  <si>
     <t>ON-MAIN-687b8c8d</t>
   </si>
   <si>
@@ -367,6 +439,18 @@
     <t>QC-MAIN-9de9bb0d</t>
   </si>
   <si>
+    <t>QC-MAIN-e51eda66</t>
+  </si>
+  <si>
+    <t>ON-MAIN-1f126a43</t>
+  </si>
+  <si>
+    <t>NU-MAIN-8b0264c9</t>
+  </si>
+  <si>
+    <t>BC-MAIN-ed23117f</t>
+  </si>
+  <si>
     <t>ON-MAIN-fefeaee4</t>
   </si>
   <si>
@@ -382,12 +466,21 @@
     <t>ON-MAIN-7607a50e</t>
   </si>
   <si>
+    <t>GRP-0a2c0d69</t>
+  </si>
+  <si>
     <t>GRP-0d911886</t>
   </si>
   <si>
+    <t>GRP-147b3123</t>
+  </si>
+  <si>
     <t>CMP-7e360a1f</t>
   </si>
   <si>
+    <t>CMP-6265c407</t>
+  </si>
+  <si>
     <t>CMP-3d2c4955</t>
   </si>
   <si>
@@ -397,15 +490,24 @@
     <t>CMP-3a4ccc7f</t>
   </si>
   <si>
+    <t>CMP-fa032e20</t>
+  </si>
+  <si>
     <t>CMP-d94be190</t>
   </si>
   <si>
+    <t>CMP-48a36546</t>
+  </si>
+  <si>
     <t>CMP-3d0a95b7</t>
   </si>
   <si>
     <t>HeclaMiningCompany_SR_2023</t>
   </si>
   <si>
+    <t>AgnicoEagleMinesLimited_2023-Sustainability-Performance_data</t>
+  </si>
+  <si>
     <t>WesdomeGoldMinesLtd._ESG_data_2023</t>
   </si>
   <si>
@@ -415,15 +517,27 @@
     <t>AlamosGoldInc_Data_2023</t>
   </si>
   <si>
+    <t>CenterraGoldInc_Data</t>
+  </si>
+  <si>
     <t>NewGoldInc_2023-New-Gold-ESG-Data-Factbook</t>
   </si>
   <si>
+    <t>NewGoldInc_ESG_data_2023</t>
+  </si>
+  <si>
+    <t>PanAmericanSilverCorp_ESG_data_2023</t>
+  </si>
+  <si>
     <t>IAMGOLDCorporation_2023_iamgold-esg-performance-data-final_protected</t>
   </si>
   <si>
     <t>lbs→t</t>
   </si>
   <si>
+    <t>unknown_unit</t>
+  </si>
+  <si>
     <t>L×density→t</t>
   </si>
   <si>
@@ -431,6 +545,9 @@
   </si>
   <si>
     <t>lbs×0.453592/1000</t>
+  </si>
+  <si>
+    <t>no rule for this unit</t>
   </si>
   <si>
     <t>reported in tonnes</t>
@@ -806,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -864,37 +981,37 @@
         <v>2023</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="F2">
         <v>6543598</v>
       </c>
       <c r="G2" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="J2" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="K2" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="L2">
         <v>2968.123704016</v>
       </c>
       <c r="M2" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="N2" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -908,37 +1025,34 @@
         <v>2023</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F3">
-        <v>1211</v>
-      </c>
-      <c r="G3" t="s">
-        <v>110</v>
+        <v>65074</v>
       </c>
       <c r="H3" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="J3" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="K3" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="L3">
-        <v>1211</v>
+        <v>16268.5</v>
       </c>
       <c r="M3" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="N3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -952,34 +1066,37 @@
         <v>2023</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F4">
-        <v>27374</v>
+        <v>1211</v>
+      </c>
+      <c r="G4" t="s">
+        <v>130</v>
       </c>
       <c r="H4" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="J4" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="K4" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="L4">
-        <v>27374</v>
+        <v>1211</v>
       </c>
       <c r="M4" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N4" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -993,37 +1110,34 @@
         <v>2023</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F5">
-        <v>3039.9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>110</v>
+        <v>27374</v>
       </c>
       <c r="H5" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="J5" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="K5" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L5">
-        <v>3039.9</v>
+        <v>27374</v>
       </c>
       <c r="M5" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N5" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
@@ -1037,34 +1151,37 @@
         <v>2023</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F6">
-        <v>2229</v>
+        <v>3039.9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>130</v>
       </c>
       <c r="H6" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="J6" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="K6" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L6">
-        <v>2229</v>
+        <v>3039.9</v>
       </c>
       <c r="M6" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N6" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -1078,34 +1195,34 @@
         <v>2023</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="F7">
-        <v>380.687</v>
+        <v>2229</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="J7" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="K7" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L7">
-        <v>335.00456</v>
+        <v>2229</v>
       </c>
       <c r="M7" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="N7" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
@@ -1119,34 +1236,34 @@
         <v>2023</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="F8">
-        <v>26575</v>
+        <v>380.687</v>
       </c>
       <c r="H8" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="J8" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="K8" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L8">
-        <v>40.12825</v>
+        <v>335.00456</v>
       </c>
       <c r="M8" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="N8" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -1160,34 +1277,34 @@
         <v>2023</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="F9">
-        <v>838.8</v>
+        <v>26575</v>
       </c>
       <c r="H9" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="J9" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="K9" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L9">
-        <v>838.8</v>
+        <v>40.12825</v>
       </c>
       <c r="M9" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="N9" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -1201,34 +1318,34 @@
         <v>2023</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F10">
-        <v>73.95999999999999</v>
+        <v>838.8</v>
       </c>
       <c r="H10" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="J10" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="K10" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L10">
-        <v>0.1360864</v>
+        <v>838.8</v>
       </c>
       <c r="M10" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="N10" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
@@ -1242,34 +1359,34 @@
         <v>2023</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="F11">
-        <v>241.250566996281</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="H11" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="J11" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="K11" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L11">
-        <v>241.250566996281</v>
+        <v>0.1360864</v>
       </c>
       <c r="M11" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="N11" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
@@ -1283,34 +1400,34 @@
         <v>2023</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F12">
-        <v>486.3</v>
+        <v>241.250566996281</v>
       </c>
       <c r="H12" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="J12" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="K12" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L12">
-        <v>486.3</v>
+        <v>241.250566996281</v>
       </c>
       <c r="M12" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N12" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -1324,34 +1441,34 @@
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F13">
-        <v>245</v>
+        <v>11047</v>
       </c>
       <c r="H13" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="J13" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="K13" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="L13">
-        <v>245</v>
+        <v>2761.75</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -1365,37 +1482,34 @@
         <v>2023</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="F14">
-        <v>511210</v>
-      </c>
-      <c r="G14" t="s">
-        <v>110</v>
+        <v>486.3</v>
       </c>
       <c r="H14" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="J14" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="K14" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="L14">
-        <v>231.88076632</v>
+        <v>486.3</v>
       </c>
       <c r="M14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="N14" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -1409,37 +1523,34 @@
         <v>2023</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F15">
-        <v>506</v>
-      </c>
-      <c r="G15" t="s">
-        <v>110</v>
+        <v>245</v>
       </c>
       <c r="H15" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="J15" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="K15" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="L15">
-        <v>506</v>
+        <v>245</v>
       </c>
       <c r="M15" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
@@ -1453,34 +1564,37 @@
         <v>2023</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="F16">
-        <v>9417.6</v>
+        <v>511210</v>
+      </c>
+      <c r="G16" t="s">
+        <v>130</v>
       </c>
       <c r="H16" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="J16" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="K16" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="L16">
-        <v>9417.6</v>
+        <v>231.88076632</v>
       </c>
       <c r="M16" t="s">
-        <v>106</v>
+        <v>172</v>
       </c>
       <c r="N16" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -1494,37 +1608,37 @@
         <v>2023</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F17">
-        <v>726.071</v>
+        <v>506</v>
       </c>
       <c r="G17" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H17" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="J17" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="K17" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="L17">
-        <v>726.071</v>
+        <v>506</v>
       </c>
       <c r="M17" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N17" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -1538,34 +1652,34 @@
         <v>2023</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="F18">
-        <v>57.2</v>
+        <v>6280</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="J18" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="K18" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="L18">
-        <v>68.068</v>
+        <v>1570</v>
       </c>
       <c r="M18" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="N18" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -1579,34 +1693,34 @@
         <v>2023</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F19">
-        <v>924.081</v>
+        <v>82576</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="J19" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="K19" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="L19">
-        <v>924.081</v>
+        <v>20644</v>
       </c>
       <c r="M19" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="N19" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -1620,34 +1734,34 @@
         <v>2023</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="F20">
-        <v>336.521</v>
-      </c>
-      <c r="H20" t="s">
-        <v>117</v>
+        <v>45318</v>
+      </c>
+      <c r="I20" t="s">
+        <v>150</v>
       </c>
       <c r="J20" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="K20" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="L20">
-        <v>296.13848</v>
+        <v>11329.5</v>
       </c>
       <c r="M20" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="N20" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -1661,34 +1775,34 @@
         <v>2023</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F21">
-        <v>390.003</v>
+        <v>18198</v>
       </c>
       <c r="H21" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="J21" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="K21" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="L21">
-        <v>390.003</v>
+        <v>4549.5</v>
       </c>
       <c r="M21" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="N21" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -1702,34 +1816,37 @@
         <v>2023</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F22">
-        <v>100.705343372947</v>
+        <v>2587.5</v>
+      </c>
+      <c r="G22" t="s">
+        <v>131</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="J22" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="K22" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="L22">
-        <v>100.705343372947</v>
+        <v>646.875</v>
       </c>
       <c r="M22" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="N22" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -1743,34 +1860,34 @@
         <v>2023</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F23">
-        <v>980</v>
+        <v>9417.6</v>
       </c>
       <c r="H23" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="J23" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K23" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L23">
-        <v>980</v>
+        <v>9417.6</v>
       </c>
       <c r="M23" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N23" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -1784,34 +1901,37 @@
         <v>2023</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F24">
-        <v>179</v>
+        <v>726.071</v>
+      </c>
+      <c r="G24" t="s">
+        <v>130</v>
       </c>
       <c r="H24" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="J24" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K24" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L24">
-        <v>179</v>
+        <v>726.071</v>
       </c>
       <c r="M24" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N24" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -1825,34 +1945,34 @@
         <v>2023</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F25">
-        <v>38000</v>
+        <v>57.2</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="J25" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K25" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L25">
-        <v>38</v>
+        <v>68.068</v>
       </c>
       <c r="M25" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="N25" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -1866,34 +1986,34 @@
         <v>2023</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F26">
-        <v>192</v>
+        <v>924.081</v>
       </c>
       <c r="H26" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="J26" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K26" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L26">
-        <v>192</v>
+        <v>924.081</v>
       </c>
       <c r="M26" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N26" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
@@ -1907,34 +2027,34 @@
         <v>2023</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="F27">
-        <v>2724</v>
+        <v>336.521</v>
       </c>
       <c r="H27" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="J27" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K27" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L27">
-        <v>2724</v>
+        <v>296.13848</v>
       </c>
       <c r="M27" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="N27" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
@@ -1948,34 +2068,34 @@
         <v>2023</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E28" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F28">
-        <v>55</v>
+        <v>390.003</v>
       </c>
       <c r="H28" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="J28" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K28" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L28">
-        <v>55</v>
+        <v>390.003</v>
       </c>
       <c r="M28" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N28" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
@@ -1989,34 +2109,34 @@
         <v>2023</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F29">
-        <v>583</v>
+        <v>100.705343372947</v>
       </c>
       <c r="H29" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="J29" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K29" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L29">
-        <v>583</v>
+        <v>100.705343372947</v>
       </c>
       <c r="M29" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O29" t="b">
         <v>0</v>
@@ -2030,34 +2150,34 @@
         <v>2023</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F30">
-        <v>12578</v>
-      </c>
-      <c r="I30" t="s">
-        <v>122</v>
+        <v>980</v>
+      </c>
+      <c r="H30" t="s">
+        <v>146</v>
       </c>
       <c r="J30" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="K30" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="L30">
-        <v>12578</v>
+        <v>980</v>
       </c>
       <c r="M30" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N30" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O30" t="b">
         <v>0</v>
@@ -2071,37 +2191,34 @@
         <v>2023</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F31">
-        <v>1932.222</v>
-      </c>
-      <c r="G31" t="s">
-        <v>110</v>
-      </c>
-      <c r="I31" t="s">
-        <v>122</v>
+        <v>179</v>
+      </c>
+      <c r="H31" t="s">
+        <v>146</v>
       </c>
       <c r="J31" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="K31" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="L31">
-        <v>1932.222</v>
+        <v>179</v>
       </c>
       <c r="M31" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N31" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
@@ -2115,34 +2232,34 @@
         <v>2023</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="F32">
-        <v>2.255</v>
-      </c>
-      <c r="I32" t="s">
-        <v>122</v>
+        <v>38000</v>
+      </c>
+      <c r="H32" t="s">
+        <v>146</v>
       </c>
       <c r="J32" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="K32" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="L32">
-        <v>2.68345</v>
+        <v>38</v>
       </c>
       <c r="M32" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="N32" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
@@ -2156,34 +2273,34 @@
         <v>2023</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E33" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="F33">
-        <v>4346.921</v>
-      </c>
-      <c r="I33" t="s">
-        <v>122</v>
+        <v>522600</v>
+      </c>
+      <c r="H33" t="s">
+        <v>146</v>
       </c>
       <c r="J33" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="K33" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="L33">
-        <v>4346.921</v>
+        <v>522.6</v>
       </c>
       <c r="M33" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="N33" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
@@ -2197,34 +2314,34 @@
         <v>2023</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="F34">
-        <v>619.366</v>
-      </c>
-      <c r="I34" t="s">
-        <v>122</v>
+        <v>192</v>
+      </c>
+      <c r="H34" t="s">
+        <v>146</v>
       </c>
       <c r="J34" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="K34" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="L34">
-        <v>545.0420799999999</v>
+        <v>192</v>
       </c>
       <c r="M34" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="N34" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
@@ -2238,34 +2355,34 @@
         <v>2023</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E35" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F35">
-        <v>175</v>
-      </c>
-      <c r="I35" t="s">
-        <v>122</v>
+        <v>2724</v>
+      </c>
+      <c r="H35" t="s">
+        <v>146</v>
       </c>
       <c r="J35" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="K35" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="L35">
-        <v>0.26425</v>
+        <v>2724</v>
       </c>
       <c r="M35" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="N35" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
@@ -2279,34 +2396,34 @@
         <v>2023</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="E36" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F36">
-        <v>734.521</v>
-      </c>
-      <c r="I36" t="s">
-        <v>122</v>
+        <v>55</v>
+      </c>
+      <c r="H36" t="s">
+        <v>146</v>
       </c>
       <c r="J36" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="K36" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="L36">
-        <v>734.521</v>
+        <v>55</v>
       </c>
       <c r="M36" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N36" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
@@ -2320,34 +2437,34 @@
         <v>2023</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E37" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F37">
-        <v>5</v>
-      </c>
-      <c r="I37" t="s">
-        <v>122</v>
+        <v>583</v>
+      </c>
+      <c r="H37" t="s">
+        <v>146</v>
       </c>
       <c r="J37" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="K37" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="L37">
-        <v>0.009200000000000002</v>
+        <v>583</v>
       </c>
       <c r="M37" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="N37" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
@@ -2361,34 +2478,34 @@
         <v>2023</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E38" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F38">
-        <v>626.983579787717</v>
+        <v>12578</v>
       </c>
       <c r="I38" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="J38" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="K38" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L38">
-        <v>626.983579787717</v>
+        <v>12578</v>
       </c>
       <c r="M38" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N38" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
@@ -2402,34 +2519,37 @@
         <v>2023</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F39">
-        <v>5977.02</v>
-      </c>
-      <c r="H39" t="s">
-        <v>119</v>
+        <v>1932.222</v>
+      </c>
+      <c r="G39" t="s">
+        <v>130</v>
+      </c>
+      <c r="I39" t="s">
+        <v>151</v>
       </c>
       <c r="J39" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K39" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L39">
-        <v>5977.02</v>
+        <v>1932.222</v>
       </c>
       <c r="M39" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N39" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O39" t="b">
         <v>0</v>
@@ -2443,34 +2563,34 @@
         <v>2023</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E40" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="F40">
-        <v>2819.39</v>
-      </c>
-      <c r="H40" t="s">
-        <v>119</v>
+        <v>2.255</v>
+      </c>
+      <c r="I40" t="s">
+        <v>151</v>
       </c>
       <c r="J40" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K40" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L40">
-        <v>2819.39</v>
+        <v>2.68345</v>
       </c>
       <c r="M40" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="N40" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
@@ -2484,34 +2604,34 @@
         <v>2023</v>
       </c>
       <c r="C41" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E41" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="F41">
-        <v>231239.82</v>
-      </c>
-      <c r="H41" t="s">
-        <v>119</v>
+        <v>4346.921</v>
+      </c>
+      <c r="I41" t="s">
+        <v>151</v>
       </c>
       <c r="J41" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K41" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L41">
-        <v>231.23982</v>
+        <v>4346.921</v>
       </c>
       <c r="M41" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="N41" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
@@ -2525,34 +2645,34 @@
         <v>2023</v>
       </c>
       <c r="C42" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E42" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="F42">
-        <v>526.21</v>
-      </c>
-      <c r="H42" t="s">
-        <v>119</v>
+        <v>619.366</v>
+      </c>
+      <c r="I42" t="s">
+        <v>151</v>
       </c>
       <c r="J42" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K42" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L42">
-        <v>526.21</v>
+        <v>545.0420799999999</v>
       </c>
       <c r="M42" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="N42" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
@@ -2566,34 +2686,34 @@
         <v>2023</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E43" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="F43">
-        <v>2269.57</v>
-      </c>
-      <c r="H43" t="s">
-        <v>119</v>
+        <v>175</v>
+      </c>
+      <c r="I43" t="s">
+        <v>151</v>
       </c>
       <c r="J43" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K43" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L43">
-        <v>2269.57</v>
+        <v>0.26425</v>
       </c>
       <c r="M43" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="N43" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="O43" t="b">
         <v>0</v>
@@ -2607,34 +2727,34 @@
         <v>2023</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F44">
-        <v>149.1</v>
-      </c>
-      <c r="H44" t="s">
-        <v>119</v>
+        <v>734.521</v>
+      </c>
+      <c r="I44" t="s">
+        <v>151</v>
       </c>
       <c r="J44" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K44" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L44">
-        <v>149.1</v>
+        <v>734.521</v>
       </c>
       <c r="M44" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N44" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O44" t="b">
         <v>0</v>
@@ -2648,34 +2768,34 @@
         <v>2023</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D45" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E45" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="F45">
-        <v>6390.4</v>
-      </c>
-      <c r="H45" t="s">
-        <v>119</v>
+        <v>5</v>
+      </c>
+      <c r="I45" t="s">
+        <v>151</v>
       </c>
       <c r="J45" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K45" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L45">
-        <v>6390.4</v>
+        <v>0.009200000000000002</v>
       </c>
       <c r="M45" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="N45" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="O45" t="b">
         <v>0</v>
@@ -2689,34 +2809,34 @@
         <v>2023</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E46" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F46">
-        <v>35.4</v>
-      </c>
-      <c r="H46" t="s">
-        <v>120</v>
+        <v>626.983579787717</v>
+      </c>
+      <c r="I46" t="s">
+        <v>151</v>
       </c>
       <c r="J46" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="K46" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="L46">
-        <v>35.4</v>
+        <v>626.983579787717</v>
       </c>
       <c r="M46" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N46" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O46" t="b">
         <v>0</v>
@@ -2730,34 +2850,34 @@
         <v>2023</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E47" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F47">
-        <v>60.4</v>
+        <v>5977.02</v>
       </c>
       <c r="H47" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="J47" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K47" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="L47">
-        <v>60.4</v>
+        <v>5977.02</v>
       </c>
       <c r="M47" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N47" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O47" t="b">
         <v>0</v>
@@ -2771,34 +2891,34 @@
         <v>2023</v>
       </c>
       <c r="C48" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E48" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F48">
-        <v>86.59999999999999</v>
+        <v>2819.39</v>
       </c>
       <c r="H48" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="J48" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K48" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="L48">
-        <v>86.59999999999999</v>
+        <v>2819.39</v>
       </c>
       <c r="M48" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N48" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O48" t="b">
         <v>0</v>
@@ -2812,34 +2932,34 @@
         <v>2023</v>
       </c>
       <c r="C49" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E49" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="F49">
-        <v>1.5</v>
+        <v>231239.82</v>
       </c>
       <c r="H49" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="J49" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K49" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="L49">
-        <v>1.5</v>
+        <v>231.23982</v>
       </c>
       <c r="M49" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="N49" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="O49" t="b">
         <v>0</v>
@@ -2853,34 +2973,34 @@
         <v>2023</v>
       </c>
       <c r="C50" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E50" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F50">
-        <v>399.3</v>
+        <v>526.21</v>
       </c>
       <c r="H50" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="J50" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K50" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="L50">
-        <v>399.3</v>
+        <v>526.21</v>
       </c>
       <c r="M50" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N50" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O50" t="b">
         <v>0</v>
@@ -2894,37 +3014,34 @@
         <v>2023</v>
       </c>
       <c r="C51" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="E51" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F51">
-        <v>1483.4</v>
-      </c>
-      <c r="G51" t="s">
-        <v>110</v>
+        <v>2269.57</v>
       </c>
       <c r="H51" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="J51" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K51" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="L51">
-        <v>1483.4</v>
+        <v>2269.57</v>
       </c>
       <c r="M51" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N51" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O51" t="b">
         <v>0</v>
@@ -2938,34 +3055,34 @@
         <v>2023</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D52" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E52" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="F52">
-        <v>46.2</v>
+        <v>14805627</v>
       </c>
       <c r="H52" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="J52" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K52" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="L52">
-        <v>46.2</v>
+        <v>14805.627</v>
       </c>
       <c r="M52" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="N52" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="O52" t="b">
         <v>0</v>
@@ -2979,34 +3096,34 @@
         <v>2023</v>
       </c>
       <c r="C53" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E53" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F53">
-        <v>4.5</v>
+        <v>149.1</v>
       </c>
       <c r="H53" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="J53" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K53" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="L53">
-        <v>4.5</v>
+        <v>149.1</v>
       </c>
       <c r="M53" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N53" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O53" t="b">
         <v>0</v>
@@ -3020,34 +3137,34 @@
         <v>2023</v>
       </c>
       <c r="C54" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E54" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F54">
-        <v>200.2</v>
+        <v>6390.4</v>
       </c>
       <c r="H54" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="J54" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K54" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="L54">
-        <v>200.2</v>
+        <v>6390.4</v>
       </c>
       <c r="M54" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N54" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O54" t="b">
         <v>0</v>
@@ -3061,34 +3178,34 @@
         <v>2023</v>
       </c>
       <c r="C55" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D55" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="E55" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F55">
-        <v>5069.3</v>
-      </c>
-      <c r="H55" t="s">
-        <v>120</v>
+        <v>20.7</v>
+      </c>
+      <c r="I55" t="s">
+        <v>152</v>
       </c>
       <c r="J55" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="K55" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="L55">
-        <v>5069.3</v>
+        <v>6.9</v>
       </c>
       <c r="M55" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="N55" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="O55" t="b">
         <v>0</v>
@@ -3102,34 +3219,34 @@
         <v>2023</v>
       </c>
       <c r="C56" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E56" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F56">
-        <v>18.9</v>
-      </c>
-      <c r="H56" t="s">
-        <v>120</v>
+        <v>4889.799999999999</v>
+      </c>
+      <c r="I56" t="s">
+        <v>152</v>
       </c>
       <c r="J56" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="K56" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="L56">
-        <v>18.9</v>
+        <v>1629.933333333333</v>
       </c>
       <c r="M56" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="N56" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="O56" t="b">
         <v>0</v>
@@ -3143,34 +3260,37 @@
         <v>2023</v>
       </c>
       <c r="C57" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D57" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E57" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F57">
-        <v>539</v>
-      </c>
-      <c r="H57" t="s">
-        <v>120</v>
+        <v>2026.3</v>
+      </c>
+      <c r="G57" t="s">
+        <v>132</v>
+      </c>
+      <c r="I57" t="s">
+        <v>152</v>
       </c>
       <c r="J57" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="K57" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="L57">
-        <v>539</v>
+        <v>675.4333333333334</v>
       </c>
       <c r="M57" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="N57" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="O57" t="b">
         <v>0</v>
@@ -3184,34 +3304,37 @@
         <v>2023</v>
       </c>
       <c r="C58" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E58" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F58">
-        <v>8.1</v>
+        <v>1530.9</v>
+      </c>
+      <c r="G58" t="s">
+        <v>132</v>
       </c>
       <c r="H58" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="J58" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="K58" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L58">
-        <v>8.1</v>
+        <v>665.608695652174</v>
       </c>
       <c r="M58" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="N58" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="O58" t="b">
         <v>0</v>
@@ -3225,37 +3348,34 @@
         <v>2023</v>
       </c>
       <c r="C59" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D59" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="E59" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F59">
-        <v>2599.5</v>
-      </c>
-      <c r="G59" t="s">
-        <v>110</v>
+        <v>35.4</v>
       </c>
       <c r="H59" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="J59" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="K59" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="L59">
-        <v>2599.5</v>
+        <v>35.4</v>
       </c>
       <c r="M59" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N59" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="O59" t="b">
         <v>0</v>
@@ -3269,36 +3389,619 @@
         <v>2023</v>
       </c>
       <c r="C60" t="s">
+        <v>88</v>
+      </c>
+      <c r="D60" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60" t="s">
+        <v>126</v>
+      </c>
+      <c r="F60">
+        <v>60.4</v>
+      </c>
+      <c r="H60" t="s">
+        <v>148</v>
+      </c>
+      <c r="J60" t="s">
+        <v>161</v>
+      </c>
+      <c r="K60" t="s">
+        <v>171</v>
+      </c>
+      <c r="L60">
+        <v>60.4</v>
+      </c>
+      <c r="M60" t="s">
+        <v>126</v>
+      </c>
+      <c r="N60" t="s">
+        <v>178</v>
+      </c>
+      <c r="O60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" t="s">
         <v>74</v>
       </c>
-      <c r="D60" t="s">
+      <c r="B61">
+        <v>2023</v>
+      </c>
+      <c r="C61" t="s">
+        <v>88</v>
+      </c>
+      <c r="D61" t="s">
+        <v>110</v>
+      </c>
+      <c r="E61" t="s">
+        <v>126</v>
+      </c>
+      <c r="F61">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="H61" t="s">
+        <v>148</v>
+      </c>
+      <c r="J61" t="s">
+        <v>161</v>
+      </c>
+      <c r="K61" t="s">
+        <v>171</v>
+      </c>
+      <c r="L61">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="M61" t="s">
+        <v>126</v>
+      </c>
+      <c r="N61" t="s">
+        <v>178</v>
+      </c>
+      <c r="O61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+      <c r="B62">
+        <v>2023</v>
+      </c>
+      <c r="C62" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" t="s">
+        <v>117</v>
+      </c>
+      <c r="E62" t="s">
+        <v>126</v>
+      </c>
+      <c r="F62">
+        <v>1.5</v>
+      </c>
+      <c r="H62" t="s">
+        <v>148</v>
+      </c>
+      <c r="J62" t="s">
+        <v>161</v>
+      </c>
+      <c r="K62" t="s">
+        <v>171</v>
+      </c>
+      <c r="L62">
+        <v>1.5</v>
+      </c>
+      <c r="M62" t="s">
+        <v>126</v>
+      </c>
+      <c r="N62" t="s">
+        <v>178</v>
+      </c>
+      <c r="O62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+      <c r="B63">
+        <v>2023</v>
+      </c>
+      <c r="C63" t="s">
+        <v>88</v>
+      </c>
+      <c r="D63" t="s">
+        <v>111</v>
+      </c>
+      <c r="E63" t="s">
+        <v>126</v>
+      </c>
+      <c r="F63">
+        <v>399.3</v>
+      </c>
+      <c r="H63" t="s">
+        <v>148</v>
+      </c>
+      <c r="J63" t="s">
+        <v>161</v>
+      </c>
+      <c r="K63" t="s">
+        <v>171</v>
+      </c>
+      <c r="L63">
+        <v>399.3</v>
+      </c>
+      <c r="M63" t="s">
+        <v>126</v>
+      </c>
+      <c r="N63" t="s">
+        <v>178</v>
+      </c>
+      <c r="O63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64">
+        <v>2023</v>
+      </c>
+      <c r="C64" t="s">
+        <v>88</v>
+      </c>
+      <c r="D64" t="s">
+        <v>118</v>
+      </c>
+      <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64">
+        <v>4260.6</v>
+      </c>
+      <c r="G64" t="s">
+        <v>132</v>
+      </c>
+      <c r="H64" t="s">
+        <v>148</v>
+      </c>
+      <c r="J64" t="s">
+        <v>161</v>
+      </c>
+      <c r="K64" t="s">
+        <v>171</v>
+      </c>
+      <c r="L64">
+        <v>1420.2</v>
+      </c>
+      <c r="M64" t="s">
+        <v>173</v>
+      </c>
+      <c r="N64" t="s">
+        <v>177</v>
+      </c>
+      <c r="O64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65">
+        <v>2023</v>
+      </c>
+      <c r="C65" t="s">
+        <v>88</v>
+      </c>
+      <c r="D65" t="s">
+        <v>90</v>
+      </c>
+      <c r="E65" t="s">
+        <v>126</v>
+      </c>
+      <c r="F65">
+        <v>1483.4</v>
+      </c>
+      <c r="G65" t="s">
+        <v>130</v>
+      </c>
+      <c r="H65" t="s">
+        <v>148</v>
+      </c>
+      <c r="J65" t="s">
+        <v>161</v>
+      </c>
+      <c r="K65" t="s">
+        <v>171</v>
+      </c>
+      <c r="L65">
+        <v>1483.4</v>
+      </c>
+      <c r="M65" t="s">
+        <v>126</v>
+      </c>
+      <c r="N65" t="s">
+        <v>178</v>
+      </c>
+      <c r="O65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66">
+        <v>2023</v>
+      </c>
+      <c r="C66" t="s">
+        <v>88</v>
+      </c>
+      <c r="D66" t="s">
+        <v>105</v>
+      </c>
+      <c r="E66" t="s">
+        <v>126</v>
+      </c>
+      <c r="F66">
+        <v>46.2</v>
+      </c>
+      <c r="H66" t="s">
+        <v>148</v>
+      </c>
+      <c r="J66" t="s">
+        <v>161</v>
+      </c>
+      <c r="K66" t="s">
+        <v>171</v>
+      </c>
+      <c r="L66">
+        <v>46.2</v>
+      </c>
+      <c r="M66" t="s">
+        <v>126</v>
+      </c>
+      <c r="N66" t="s">
+        <v>178</v>
+      </c>
+      <c r="O66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67">
+        <v>2023</v>
+      </c>
+      <c r="C67" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" t="s">
+        <v>119</v>
+      </c>
+      <c r="E67" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67">
+        <v>4.5</v>
+      </c>
+      <c r="H67" t="s">
+        <v>148</v>
+      </c>
+      <c r="J67" t="s">
+        <v>161</v>
+      </c>
+      <c r="K67" t="s">
+        <v>171</v>
+      </c>
+      <c r="L67">
+        <v>4.5</v>
+      </c>
+      <c r="M67" t="s">
+        <v>126</v>
+      </c>
+      <c r="N67" t="s">
+        <v>178</v>
+      </c>
+      <c r="O67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68">
+        <v>2023</v>
+      </c>
+      <c r="C68" t="s">
+        <v>88</v>
+      </c>
+      <c r="D68" t="s">
+        <v>120</v>
+      </c>
+      <c r="E68" t="s">
+        <v>126</v>
+      </c>
+      <c r="F68">
+        <v>200.2</v>
+      </c>
+      <c r="H68" t="s">
+        <v>148</v>
+      </c>
+      <c r="J68" t="s">
+        <v>161</v>
+      </c>
+      <c r="K68" t="s">
+        <v>171</v>
+      </c>
+      <c r="L68">
+        <v>200.2</v>
+      </c>
+      <c r="M68" t="s">
+        <v>126</v>
+      </c>
+      <c r="N68" t="s">
+        <v>178</v>
+      </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69">
+        <v>2023</v>
+      </c>
+      <c r="C69" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69" t="s">
+        <v>93</v>
+      </c>
+      <c r="E69" t="s">
+        <v>126</v>
+      </c>
+      <c r="F69">
+        <v>5069.3</v>
+      </c>
+      <c r="H69" t="s">
+        <v>148</v>
+      </c>
+      <c r="J69" t="s">
+        <v>161</v>
+      </c>
+      <c r="K69" t="s">
+        <v>171</v>
+      </c>
+      <c r="L69">
+        <v>5069.3</v>
+      </c>
+      <c r="M69" t="s">
+        <v>126</v>
+      </c>
+      <c r="N69" t="s">
+        <v>178</v>
+      </c>
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70">
+        <v>2023</v>
+      </c>
+      <c r="C70" t="s">
+        <v>88</v>
+      </c>
+      <c r="D70" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" t="s">
+        <v>126</v>
+      </c>
+      <c r="F70">
+        <v>18.9</v>
+      </c>
+      <c r="H70" t="s">
+        <v>148</v>
+      </c>
+      <c r="J70" t="s">
+        <v>161</v>
+      </c>
+      <c r="K70" t="s">
+        <v>171</v>
+      </c>
+      <c r="L70">
+        <v>18.9</v>
+      </c>
+      <c r="M70" t="s">
+        <v>126</v>
+      </c>
+      <c r="N70" t="s">
+        <v>178</v>
+      </c>
+      <c r="O70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71">
+        <v>2023</v>
+      </c>
+      <c r="C71" t="s">
+        <v>88</v>
+      </c>
+      <c r="D71" t="s">
+        <v>122</v>
+      </c>
+      <c r="E71" t="s">
+        <v>126</v>
+      </c>
+      <c r="F71">
+        <v>539</v>
+      </c>
+      <c r="H71" t="s">
+        <v>148</v>
+      </c>
+      <c r="J71" t="s">
+        <v>161</v>
+      </c>
+      <c r="K71" t="s">
+        <v>171</v>
+      </c>
+      <c r="L71">
+        <v>539</v>
+      </c>
+      <c r="M71" t="s">
+        <v>126</v>
+      </c>
+      <c r="N71" t="s">
+        <v>178</v>
+      </c>
+      <c r="O71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" t="s">
+        <v>85</v>
+      </c>
+      <c r="B72">
+        <v>2023</v>
+      </c>
+      <c r="C72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D72" t="s">
+        <v>123</v>
+      </c>
+      <c r="E72" t="s">
+        <v>126</v>
+      </c>
+      <c r="F72">
+        <v>8.1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>148</v>
+      </c>
+      <c r="J72" t="s">
+        <v>161</v>
+      </c>
+      <c r="K72" t="s">
+        <v>171</v>
+      </c>
+      <c r="L72">
+        <v>8.1</v>
+      </c>
+      <c r="M72" t="s">
+        <v>126</v>
+      </c>
+      <c r="N72" t="s">
+        <v>178</v>
+      </c>
+      <c r="O72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" t="s">
         <v>86</v>
       </c>
-      <c r="E60" t="s">
-        <v>106</v>
-      </c>
-      <c r="F60">
+      <c r="B73">
+        <v>2023</v>
+      </c>
+      <c r="C73" t="s">
+        <v>88</v>
+      </c>
+      <c r="D73" t="s">
+        <v>99</v>
+      </c>
+      <c r="E73" t="s">
+        <v>126</v>
+      </c>
+      <c r="F73">
+        <v>2599.5</v>
+      </c>
+      <c r="G73" t="s">
+        <v>130</v>
+      </c>
+      <c r="H73" t="s">
+        <v>149</v>
+      </c>
+      <c r="J73" t="s">
+        <v>157</v>
+      </c>
+      <c r="K73" t="s">
+        <v>166</v>
+      </c>
+      <c r="L73">
+        <v>2599.5</v>
+      </c>
+      <c r="M73" t="s">
+        <v>126</v>
+      </c>
+      <c r="N73" t="s">
+        <v>178</v>
+      </c>
+      <c r="O73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" t="s">
+        <v>87</v>
+      </c>
+      <c r="B74">
+        <v>2023</v>
+      </c>
+      <c r="C74" t="s">
+        <v>88</v>
+      </c>
+      <c r="D74" t="s">
+        <v>100</v>
+      </c>
+      <c r="E74" t="s">
+        <v>126</v>
+      </c>
+      <c r="F74">
         <v>1955.7</v>
       </c>
-      <c r="H60" t="s">
-        <v>121</v>
-      </c>
-      <c r="J60" t="s">
-        <v>126</v>
-      </c>
-      <c r="K60" t="s">
-        <v>132</v>
-      </c>
-      <c r="L60">
+      <c r="H74" t="s">
+        <v>149</v>
+      </c>
+      <c r="J74" t="s">
+        <v>157</v>
+      </c>
+      <c r="K74" t="s">
+        <v>166</v>
+      </c>
+      <c r="L74">
         <v>1955.7</v>
       </c>
-      <c r="M60" t="s">
-        <v>106</v>
-      </c>
-      <c r="N60" t="s">
-        <v>139</v>
-      </c>
-      <c r="O60" t="b">
+      <c r="M74" t="s">
+        <v>126</v>
+      </c>
+      <c r="N74" t="s">
+        <v>178</v>
+      </c>
+      <c r="O74" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/MetalliCan/pre_cleaned_data/material_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/material_df.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_23F921ED83CB883F5B2C4CE9ED4E8C106C1A24BF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18EB9B47-800B-42FA-AA97-F2157AC98ED2}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -571,8 +577,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -635,13 +641,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -679,7 +693,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -713,6 +727,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -747,9 +762,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -922,11 +938,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O74"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="180.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="69.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -973,7 +1006,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1005,7 +1038,7 @@
         <v>162</v>
       </c>
       <c r="L2">
-        <v>2968.123704016</v>
+        <v>2968.1237040159999</v>
       </c>
       <c r="M2" t="s">
         <v>172</v>
@@ -1017,7 +1050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1058,7 +1091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1102,7 +1135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1143,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1187,7 +1220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1228,7 +1261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1245,7 +1278,7 @@
         <v>127</v>
       </c>
       <c r="F8">
-        <v>380.687</v>
+        <v>380.68700000000001</v>
       </c>
       <c r="H8" t="s">
         <v>136</v>
@@ -1257,7 +1290,7 @@
         <v>165</v>
       </c>
       <c r="L8">
-        <v>335.00456</v>
+        <v>335.00456000000003</v>
       </c>
       <c r="M8" t="s">
         <v>174</v>
@@ -1269,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1298,7 +1331,7 @@
         <v>165</v>
       </c>
       <c r="L9">
-        <v>40.12825</v>
+        <v>40.128250000000001</v>
       </c>
       <c r="M9" t="s">
         <v>174</v>
@@ -1310,7 +1343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1351,7 +1384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1368,7 +1401,7 @@
         <v>128</v>
       </c>
       <c r="F11">
-        <v>73.95999999999999</v>
+        <v>73.959999999999994</v>
       </c>
       <c r="H11" t="s">
         <v>136</v>
@@ -1392,7 +1425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1409,7 +1442,7 @@
         <v>126</v>
       </c>
       <c r="F12">
-        <v>241.250566996281</v>
+        <v>241.25056699628101</v>
       </c>
       <c r="H12" t="s">
         <v>136</v>
@@ -1421,7 +1454,7 @@
         <v>165</v>
       </c>
       <c r="L12">
-        <v>241.250566996281</v>
+        <v>241.25056699628101</v>
       </c>
       <c r="M12" t="s">
         <v>126</v>
@@ -1433,7 +1466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1474,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1515,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1556,7 +1589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1588,7 +1621,7 @@
         <v>162</v>
       </c>
       <c r="L16">
-        <v>231.88076632</v>
+        <v>231.88076631999999</v>
       </c>
       <c r="M16" t="s">
         <v>172</v>
@@ -1600,7 +1633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1644,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1685,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1726,7 +1759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1767,7 +1800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1808,7 +1841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -1852,7 +1885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1893,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1910,7 +1943,7 @@
         <v>126</v>
       </c>
       <c r="F24">
-        <v>726.071</v>
+        <v>726.07100000000003</v>
       </c>
       <c r="G24" t="s">
         <v>130</v>
@@ -1925,7 +1958,7 @@
         <v>165</v>
       </c>
       <c r="L24">
-        <v>726.071</v>
+        <v>726.07100000000003</v>
       </c>
       <c r="M24" t="s">
         <v>126</v>
@@ -1937,7 +1970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1966,7 +1999,7 @@
         <v>165</v>
       </c>
       <c r="L25">
-        <v>68.068</v>
+        <v>68.067999999999998</v>
       </c>
       <c r="M25" t="s">
         <v>174</v>
@@ -1978,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1995,7 +2028,7 @@
         <v>126</v>
       </c>
       <c r="F26">
-        <v>924.081</v>
+        <v>924.08100000000002</v>
       </c>
       <c r="H26" t="s">
         <v>145</v>
@@ -2007,7 +2040,7 @@
         <v>165</v>
       </c>
       <c r="L26">
-        <v>924.081</v>
+        <v>924.08100000000002</v>
       </c>
       <c r="M26" t="s">
         <v>126</v>
@@ -2019,7 +2052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -2036,7 +2069,7 @@
         <v>127</v>
       </c>
       <c r="F27">
-        <v>336.521</v>
+        <v>336.52100000000002</v>
       </c>
       <c r="H27" t="s">
         <v>145</v>
@@ -2048,7 +2081,7 @@
         <v>165</v>
       </c>
       <c r="L27">
-        <v>296.13848</v>
+        <v>296.13848000000002</v>
       </c>
       <c r="M27" t="s">
         <v>174</v>
@@ -2060,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -2077,7 +2110,7 @@
         <v>126</v>
       </c>
       <c r="F28">
-        <v>390.003</v>
+        <v>390.00299999999999</v>
       </c>
       <c r="H28" t="s">
         <v>145</v>
@@ -2089,7 +2122,7 @@
         <v>165</v>
       </c>
       <c r="L28">
-        <v>390.003</v>
+        <v>390.00299999999999</v>
       </c>
       <c r="M28" t="s">
         <v>126</v>
@@ -2101,7 +2134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -2142,7 +2175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -2183,7 +2216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -2224,7 +2257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -2265,7 +2298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -2306,7 +2339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -2347,7 +2380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -2388,7 +2421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -2429,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2470,7 +2503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -2511,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -2555,7 +2588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -2572,7 +2605,7 @@
         <v>127</v>
       </c>
       <c r="F40">
-        <v>2.255</v>
+        <v>2.2549999999999999</v>
       </c>
       <c r="I40" t="s">
         <v>151</v>
@@ -2584,7 +2617,7 @@
         <v>165</v>
       </c>
       <c r="L40">
-        <v>2.68345</v>
+        <v>2.6834500000000001</v>
       </c>
       <c r="M40" t="s">
         <v>174</v>
@@ -2596,7 +2629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -2613,7 +2646,7 @@
         <v>126</v>
       </c>
       <c r="F41">
-        <v>4346.921</v>
+        <v>4346.9210000000003</v>
       </c>
       <c r="I41" t="s">
         <v>151</v>
@@ -2625,7 +2658,7 @@
         <v>165</v>
       </c>
       <c r="L41">
-        <v>4346.921</v>
+        <v>4346.9210000000003</v>
       </c>
       <c r="M41" t="s">
         <v>126</v>
@@ -2637,7 +2670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>55</v>
       </c>
@@ -2654,7 +2687,7 @@
         <v>127</v>
       </c>
       <c r="F42">
-        <v>619.366</v>
+        <v>619.36599999999999</v>
       </c>
       <c r="I42" t="s">
         <v>151</v>
@@ -2666,7 +2699,7 @@
         <v>165</v>
       </c>
       <c r="L42">
-        <v>545.0420799999999</v>
+        <v>545.04207999999994</v>
       </c>
       <c r="M42" t="s">
         <v>174</v>
@@ -2678,7 +2711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -2707,7 +2740,7 @@
         <v>165</v>
       </c>
       <c r="L43">
-        <v>0.26425</v>
+        <v>0.26424999999999998</v>
       </c>
       <c r="M43" t="s">
         <v>174</v>
@@ -2719,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>57</v>
       </c>
@@ -2736,7 +2769,7 @@
         <v>126</v>
       </c>
       <c r="F44">
-        <v>734.521</v>
+        <v>734.52099999999996</v>
       </c>
       <c r="I44" t="s">
         <v>151</v>
@@ -2748,7 +2781,7 @@
         <v>165</v>
       </c>
       <c r="L44">
-        <v>734.521</v>
+        <v>734.52099999999996</v>
       </c>
       <c r="M44" t="s">
         <v>126</v>
@@ -2760,7 +2793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>58</v>
       </c>
@@ -2789,7 +2822,7 @@
         <v>165</v>
       </c>
       <c r="L45">
-        <v>0.009200000000000002</v>
+        <v>9.2000000000000016E-3</v>
       </c>
       <c r="M45" t="s">
         <v>174</v>
@@ -2801,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -2818,7 +2851,7 @@
         <v>126</v>
       </c>
       <c r="F46">
-        <v>626.983579787717</v>
+        <v>626.98357978771696</v>
       </c>
       <c r="I46" t="s">
         <v>151</v>
@@ -2830,7 +2863,7 @@
         <v>165</v>
       </c>
       <c r="L46">
-        <v>626.983579787717</v>
+        <v>626.98357978771696</v>
       </c>
       <c r="M46" t="s">
         <v>126</v>
@@ -2842,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -2883,7 +2916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -2924,7 +2957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>62</v>
       </c>
@@ -2953,7 +2986,7 @@
         <v>168</v>
       </c>
       <c r="L49">
-        <v>231.23982</v>
+        <v>231.23982000000001</v>
       </c>
       <c r="M49" t="s">
         <v>175</v>
@@ -2965,7 +2998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -3006,7 +3039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -3023,7 +3056,7 @@
         <v>126</v>
       </c>
       <c r="F51">
-        <v>2269.57</v>
+        <v>2269.5700000000002</v>
       </c>
       <c r="H51" t="s">
         <v>147</v>
@@ -3035,7 +3068,7 @@
         <v>168</v>
       </c>
       <c r="L51">
-        <v>2269.57</v>
+        <v>2269.5700000000002</v>
       </c>
       <c r="M51" t="s">
         <v>126</v>
@@ -3047,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>65</v>
       </c>
@@ -3088,7 +3121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -3129,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>67</v>
       </c>
@@ -3170,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>68</v>
       </c>
@@ -3211,7 +3244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -3228,7 +3261,7 @@
         <v>125</v>
       </c>
       <c r="F56">
-        <v>4889.799999999999</v>
+        <v>4889.7999999999993</v>
       </c>
       <c r="I56" t="s">
         <v>152</v>
@@ -3240,7 +3273,7 @@
         <v>170</v>
       </c>
       <c r="L56">
-        <v>1629.933333333333</v>
+        <v>1629.9333333333329</v>
       </c>
       <c r="M56" t="s">
         <v>173</v>
@@ -3252,7 +3285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>70</v>
       </c>
@@ -3284,7 +3317,7 @@
         <v>170</v>
       </c>
       <c r="L57">
-        <v>675.4333333333334</v>
+        <v>675.43333333333339</v>
       </c>
       <c r="M57" t="s">
         <v>173</v>
@@ -3296,7 +3329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>71</v>
       </c>
@@ -3328,7 +3361,7 @@
         <v>171</v>
       </c>
       <c r="L58">
-        <v>665.608695652174</v>
+        <v>665.60869565217399</v>
       </c>
       <c r="M58" t="s">
         <v>173</v>
@@ -3340,7 +3373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -3381,7 +3414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>73</v>
       </c>
@@ -3422,7 +3455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>74</v>
       </c>
@@ -3439,7 +3472,7 @@
         <v>126</v>
       </c>
       <c r="F61">
-        <v>86.59999999999999</v>
+        <v>86.6</v>
       </c>
       <c r="H61" t="s">
         <v>148</v>
@@ -3451,7 +3484,7 @@
         <v>171</v>
       </c>
       <c r="L61">
-        <v>86.59999999999999</v>
+        <v>86.6</v>
       </c>
       <c r="M61" t="s">
         <v>126</v>
@@ -3463,7 +3496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>75</v>
       </c>
@@ -3504,7 +3537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>76</v>
       </c>
@@ -3545,7 +3578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>77</v>
       </c>
@@ -3562,7 +3595,7 @@
         <v>125</v>
       </c>
       <c r="F64">
-        <v>4260.6</v>
+        <v>4260.6000000000004</v>
       </c>
       <c r="G64" t="s">
         <v>132</v>
@@ -3589,7 +3622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>78</v>
       </c>
@@ -3633,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>79</v>
       </c>
@@ -3674,7 +3707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>80</v>
       </c>
@@ -3715,7 +3748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>81</v>
       </c>
@@ -3756,7 +3789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>82</v>
       </c>
@@ -3797,7 +3830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -3814,7 +3847,7 @@
         <v>126</v>
       </c>
       <c r="F70">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="H70" t="s">
         <v>148</v>
@@ -3826,7 +3859,7 @@
         <v>171</v>
       </c>
       <c r="L70">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="M70" t="s">
         <v>126</v>
@@ -3838,7 +3871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>84</v>
       </c>
@@ -3879,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>85</v>
       </c>
@@ -3920,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>86</v>
       </c>
@@ -3964,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>87</v>
       </c>
